--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B28FF2E-9A2D-4FBF-A84C-0E90D6E6ACB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4291A58B-BE35-4741-9795-8CCC99156A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Conv. y Tick" sheetId="2" r:id="rId1"/>
+    <sheet name="Conv. y Tick" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -114,9 +114,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00\ %;\-0.00\ %;0.00\ %"/>
-    <numFmt numFmtId="165" formatCode="0.00%;\-0.00%;0.00%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -170,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -178,25 +177,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -531,13 +528,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E328B83A-1398-4710-92B2-0F52B49E44BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17233115-4901-4354-B5A2-D6FF1650C878}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
@@ -560,347 +557,346 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>1.4220623501199039</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2" s="3">
+        <v>1.4206266318537859</v>
+      </c>
+      <c r="C2" s="3">
         <v>1.4056690594515</v>
       </c>
-      <c r="D2" s="5">
-        <v>0.33601933924254634</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="4">
+        <v>0.32884004464669014</v>
+      </c>
+      <c r="E2" s="4">
         <v>0.13311608761699417</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
-        <v>1.3825575173889781</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="3">
+        <v>1.3858724301528731</v>
+      </c>
+      <c r="C3" s="3">
         <v>1.3729456384323642</v>
       </c>
-      <c r="D3" s="5">
-        <v>0.18228811079683996</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="D3" s="4">
+        <v>0.1771076463448791</v>
+      </c>
+      <c r="E3" s="4">
         <v>0.17603857566765579</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>1.3450175262894344</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="3">
+        <v>1.3454278009316007</v>
+      </c>
+      <c r="C4" s="3">
         <v>1.3143459915611815</v>
       </c>
-      <c r="D4" s="5">
-        <v>0.22275515895147796</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="D4" s="4">
+        <v>0.21919501316567253</v>
+      </c>
+      <c r="E4" s="4">
         <v>0.20968812209688123</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>1.2924198250728862</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="B5" s="3">
+        <v>1.2918108419838523</v>
+      </c>
+      <c r="C5" s="3">
         <v>1.3254151291512914</v>
       </c>
-      <c r="D5" s="5">
-        <v>8.7831609136535899E-2</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="D5" s="4">
+        <v>8.5920273517825732E-2</v>
+      </c>
+      <c r="E5" s="4">
         <v>9.7558780515243554E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>1.2607580507267029</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="B6" s="3">
+        <v>1.2623019767278845</v>
+      </c>
+      <c r="C6" s="3">
         <v>1.2475728155339807</v>
       </c>
-      <c r="D6" s="5">
-        <v>0.12764177367138335</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="D6" s="4">
+        <v>0.12386691209669017</v>
+      </c>
+      <c r="E6" s="4">
         <v>0.13061988586611914</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4">
-        <v>1.2335910511597301</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="3">
+        <v>1.2338292367399741</v>
+      </c>
+      <c r="C7" s="3">
         <v>1.2051149127354415</v>
       </c>
-      <c r="D7" s="5">
-        <v>0.10094317691209193</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D7" s="4">
+        <v>9.902004739640044E-2</v>
+      </c>
+      <c r="E7" s="4">
         <v>9.0552043562621268E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
-        <v>1.2311626321172862</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="B8" s="3">
+        <v>1.2331052895044219</v>
+      </c>
+      <c r="C8" s="3">
         <v>1.2359058565955119</v>
       </c>
-      <c r="D8" s="5">
-        <v>0.11515960579528053</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D8" s="4">
+        <v>0.11286252354048965</v>
+      </c>
+      <c r="E8" s="4">
         <v>0.10872087833615995</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
-        <v>1.2308316430020285</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="B9" s="3">
+        <v>1.2315389233540124</v>
+      </c>
+      <c r="C9" s="3">
         <v>1.228626630172275</v>
       </c>
-      <c r="D9" s="5">
-        <v>0.10148209139563606</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="4">
+        <v>9.9492284718765561E-2</v>
+      </c>
+      <c r="E9" s="4">
         <v>0.10461160142828269</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
-        <v>1.2185699762792275</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="B10" s="3">
+        <v>1.2176529588766298</v>
+      </c>
+      <c r="C10" s="3">
         <v>1.2559274755927476</v>
       </c>
-      <c r="D10" s="5">
-        <v>7.107931690632753E-2</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="D10" s="4">
+        <v>6.974954526374702E-2</v>
+      </c>
+      <c r="E10" s="4">
         <v>7.5478980981121477E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1.2108597285067872</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1.2169246130803795</v>
+      </c>
+      <c r="D11" s="4">
+        <v>9.9498754389650931E-2</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.10506989797256537</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.2103250478011471</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1.3651176825588414</v>
+      </c>
+      <c r="D12" s="4">
+        <v>9.0725106973516823E-2</v>
+      </c>
+      <c r="E12" s="4">
+        <v>8.6908633168991917E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
-        <v>1.2101745265503159</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="B13" s="3">
+        <v>1.2095063985374772</v>
+      </c>
+      <c r="C13" s="3">
         <v>1.2094943240454077</v>
       </c>
-      <c r="D11" s="5">
-        <v>9.5024700070571635E-2</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="D13" s="4">
+        <v>9.3379767148076068E-2</v>
+      </c>
+      <c r="E13" s="4">
         <v>9.7972802183913854E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1.2091743119266056</v>
-      </c>
-      <c r="C12" s="4">
-        <v>1.2169246130803795</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0.10244039973685035</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.10506989797256537</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4">
-        <v>1.2054794520547942</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1.3651176825588414</v>
-      </c>
-      <c r="D13" s="5">
-        <v>9.1675636885540007E-2</v>
-      </c>
-      <c r="E13" s="6">
-        <v>8.6908633168991917E-2</v>
-      </c>
-    </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
-        <v>1.199667221297837</v>
-      </c>
-      <c r="C14" s="4">
+      <c r="B14" s="3">
+        <v>1.2004909983633387</v>
+      </c>
+      <c r="C14" s="3">
         <v>1.2434956637758505</v>
       </c>
-      <c r="D14" s="5">
-        <v>8.7208880504969888E-2</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="D14" s="4">
+        <v>8.5382895472330911E-2</v>
+      </c>
+      <c r="E14" s="4">
         <v>8.6527360886631266E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="4">
-        <v>1.1982101425256877</v>
-      </c>
-      <c r="C15" s="4">
+      <c r="B15" s="3">
+        <v>1.197877551020408</v>
+      </c>
+      <c r="C15" s="3">
         <v>1.2041379310344826</v>
       </c>
-      <c r="D15" s="5">
-        <v>0.12836113002042204</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="D15" s="4">
+        <v>0.12569259183254669</v>
+      </c>
+      <c r="E15" s="4">
         <v>0.12276275462688589</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4">
-        <v>1.1977482678983835</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="B16" s="3">
+        <v>1.1973423805484875</v>
+      </c>
+      <c r="C16" s="3">
         <v>1.1941026236359416</v>
       </c>
-      <c r="D16" s="5">
-        <v>0.11910328703066979</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="D16" s="4">
+        <v>0.11699523683514157</v>
+      </c>
+      <c r="E16" s="4">
         <v>0.10437416696958682</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="4">
-        <v>1.1964450600184673</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B17" s="3">
+        <v>1.1960873521383077</v>
+      </c>
+      <c r="C17" s="3">
         <v>1.2261133603238867</v>
       </c>
-      <c r="D17" s="5">
-        <v>8.5787274491553947E-2</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="D17" s="4">
+        <v>8.3936379432150154E-2</v>
+      </c>
+      <c r="E17" s="4">
         <v>8.3798408848026321E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1.1889525092623781</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1.2214765100671141</v>
+      </c>
+      <c r="D18" s="4">
+        <v>8.2032437211615503E-2</v>
+      </c>
+      <c r="E18" s="4">
+        <v>8.3441602078759919E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4">
-        <v>1.1888888888888889</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="B19" s="3">
+        <v>1.1867509261276967</v>
+      </c>
+      <c r="C19" s="3">
         <v>1.2018115942028984</v>
       </c>
-      <c r="D18" s="5">
-        <v>8.9994600323980559E-2</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="D19" s="4">
+        <v>8.7911877394636018E-2</v>
+      </c>
+      <c r="E19" s="4">
         <v>8.8781664656212303E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4">
-        <v>1.1868131868131866</v>
-      </c>
-      <c r="C19" s="4">
-        <v>1.2214765100671141</v>
-      </c>
-      <c r="D19" s="5">
-        <v>8.3285665255691574E-2</v>
-      </c>
-      <c r="E19" s="6">
-        <v>8.3441602078759919E-2</v>
-      </c>
-    </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4">
-        <v>1.1749408983451537</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="B20" s="3">
+        <v>1.1752336448598131</v>
+      </c>
+      <c r="C20" s="3">
         <v>1.2132932782576042</v>
       </c>
-      <c r="D20" s="5">
-        <v>9.077642817288295E-2</v>
-      </c>
-      <c r="E20" s="6">
+      <c r="D20" s="4">
+        <v>8.8745127311934971E-2</v>
+      </c>
+      <c r="E20" s="4">
         <v>9.4379075701729515E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="8">
-        <v>1.2414344290777679</v>
-      </c>
-      <c r="C21" s="8">
+      <c r="B21" s="5">
+        <v>1.2418783911219233</v>
+      </c>
+      <c r="C21" s="5">
         <v>1.2500987751876729</v>
       </c>
-      <c r="D21" s="9">
-        <v>0.10896399016151115</v>
-      </c>
-      <c r="E21" s="10">
+      <c r="D21" s="6">
+        <v>0.10671806472596695</v>
+      </c>
+      <c r="E21" s="6">
         <v>0.10502560284352211</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4291A58B-BE35-4741-9795-8CCC99156A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2851C58-0B7B-4C09-810D-3456FBF45C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,10 +190,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4206266318537859</v>
+        <v>1.4236736736736735</v>
       </c>
       <c r="C2" s="3">
         <v>1.4056690594515</v>
       </c>
       <c r="D2" s="4">
-        <v>0.32884004464669014</v>
+        <v>0.32780968006562755</v>
       </c>
       <c r="E2" s="4">
         <v>0.13311608761699417</v>
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3858724301528731</v>
+        <v>1.3907584128578605</v>
       </c>
       <c r="C3" s="3">
         <v>1.3729456384323642</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1771076463448791</v>
+        <v>0.17628829466973614</v>
       </c>
       <c r="E3" s="4">
         <v>0.17603857566765579</v>
@@ -595,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3454278009316007</v>
+        <v>1.3465346534653464</v>
       </c>
       <c r="C4" s="3">
         <v>1.3143459915611815</v>
       </c>
       <c r="D4" s="4">
-        <v>0.21919501316567253</v>
+        <v>0.2174826967444245</v>
       </c>
       <c r="E4" s="4">
         <v>0.20968812209688123</v>
@@ -612,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2918108419838523</v>
+        <v>1.2902684563758389</v>
       </c>
       <c r="C5" s="3">
         <v>1.3254151291512914</v>
       </c>
       <c r="D5" s="4">
-        <v>8.5920273517825732E-2</v>
+        <v>8.5346062052505972E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.7558780515243554E-2</v>
@@ -629,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2623019767278845</v>
+        <v>1.2657560183932917</v>
       </c>
       <c r="C6" s="3">
         <v>1.2475728155339807</v>
       </c>
       <c r="D6" s="4">
-        <v>0.12386691209669017</v>
+        <v>0.12364755263465944</v>
       </c>
       <c r="E6" s="4">
         <v>0.13061988586611914</v>
@@ -643,36 +643,36 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2338292367399741</v>
+        <v>1.2351333976213434</v>
       </c>
       <c r="C7" s="3">
-        <v>1.2051149127354415</v>
+        <v>1.2359058565955119</v>
       </c>
       <c r="D7" s="4">
-        <v>9.902004739640044E-2</v>
+        <v>0.112328717661714</v>
       </c>
       <c r="E7" s="4">
-        <v>9.0552043562621268E-2</v>
+        <v>0.10872087833615995</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2331052895044219</v>
+        <v>1.234790726622063</v>
       </c>
       <c r="C8" s="3">
-        <v>1.2359058565955119</v>
+        <v>1.2051149127354415</v>
       </c>
       <c r="D8" s="4">
-        <v>0.11286252354048965</v>
+        <v>9.8705327661142941E-2</v>
       </c>
       <c r="E8" s="4">
-        <v>0.10872087833615995</v>
+        <v>9.0552043562621268E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -680,13 +680,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2315389233540124</v>
+        <v>1.2319288751449555</v>
       </c>
       <c r="C9" s="3">
         <v>1.228626630172275</v>
       </c>
       <c r="D9" s="4">
-        <v>9.9492284718765561E-2</v>
+        <v>9.8925471301288675E-2</v>
       </c>
       <c r="E9" s="4">
         <v>0.10461160142828269</v>
@@ -697,13 +697,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2176529588766298</v>
+        <v>1.2210355987055015</v>
       </c>
       <c r="C10" s="3">
         <v>1.2559274755927476</v>
       </c>
       <c r="D10" s="4">
-        <v>6.974954526374702E-2</v>
+        <v>6.9622820062187368E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.5478980981121477E-2</v>
@@ -714,13 +714,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2108597285067872</v>
+        <v>1.2116448326055314</v>
       </c>
       <c r="C11" s="3">
         <v>1.2169246130803795</v>
       </c>
       <c r="D11" s="4">
-        <v>9.9498754389650931E-2</v>
+        <v>9.8644535064039973E-2</v>
       </c>
       <c r="E11" s="4">
         <v>0.10506989797256537</v>
@@ -728,53 +728,53 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2103250478011471</v>
+        <v>1.211464522894093</v>
       </c>
       <c r="C12" s="3">
-        <v>1.3651176825588414</v>
+        <v>1.2094943240454077</v>
       </c>
       <c r="D12" s="4">
-        <v>9.0725106973516823E-2</v>
+        <v>9.3402108974568243E-2</v>
       </c>
       <c r="E12" s="4">
-        <v>8.6908633168991917E-2</v>
+        <v>9.7972802183913854E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2095063985374772</v>
+        <v>1.2112415071031502</v>
       </c>
       <c r="C13" s="3">
-        <v>1.2094943240454077</v>
+        <v>1.3651176825588414</v>
       </c>
       <c r="D13" s="4">
-        <v>9.3379767148076068E-2</v>
+        <v>8.9210932334141499E-2</v>
       </c>
       <c r="E13" s="4">
-        <v>9.7972802183913854E-2</v>
+        <v>8.6908633168991917E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3">
-        <v>1.2004909983633387</v>
+        <v>1.2000544365813826</v>
       </c>
       <c r="C14" s="3">
-        <v>1.2434956637758505</v>
+        <v>1.1941026236359416</v>
       </c>
       <c r="D14" s="4">
-        <v>8.5382895472330911E-2</v>
+        <v>0.11636524878852184</v>
       </c>
       <c r="E14" s="4">
-        <v>8.6527360886631266E-2</v>
+        <v>0.10437416696958682</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -782,13 +782,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1.197877551020408</v>
+        <v>1.1962369771419685</v>
       </c>
       <c r="C15" s="3">
         <v>1.2041379310344826</v>
       </c>
       <c r="D15" s="4">
-        <v>0.12569259183254669</v>
+        <v>0.12587836912055433</v>
       </c>
       <c r="E15" s="4">
         <v>0.12276275462688589</v>
@@ -796,19 +796,19 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1973423805484875</v>
+        <v>1.1961240310077519</v>
       </c>
       <c r="C16" s="3">
-        <v>1.1941026236359416</v>
+        <v>1.2434956637758505</v>
       </c>
       <c r="D16" s="4">
-        <v>0.11699523683514157</v>
+        <v>8.6322269807280513E-2</v>
       </c>
       <c r="E16" s="4">
-        <v>0.10437416696958682</v>
+        <v>8.6527360886631266E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -816,13 +816,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1960873521383077</v>
+        <v>1.1959459459459461</v>
       </c>
       <c r="C17" s="3">
         <v>1.2261133603238867</v>
       </c>
       <c r="D17" s="4">
-        <v>8.3936379432150154E-2</v>
+        <v>8.3750136906283079E-2</v>
       </c>
       <c r="E17" s="4">
         <v>8.3798408848026321E-2</v>
@@ -833,13 +833,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1889525092623781</v>
+        <v>1.191798514691637</v>
       </c>
       <c r="C18" s="3">
         <v>1.2214765100671141</v>
       </c>
       <c r="D18" s="4">
-        <v>8.2032437211615503E-2</v>
+        <v>8.1840283283124565E-2</v>
       </c>
       <c r="E18" s="4">
         <v>8.3441602078759919E-2</v>
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1867509261276967</v>
+        <v>1.1892171039041521</v>
       </c>
       <c r="C19" s="3">
         <v>1.2018115942028984</v>
       </c>
       <c r="D19" s="4">
-        <v>8.7911877394636018E-2</v>
+        <v>8.8103081150927257E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.8781664656212303E-2</v>
@@ -867,13 +867,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1752336448598131</v>
+        <v>1.1745890715237672</v>
       </c>
       <c r="C20" s="3">
         <v>1.2132932782576042</v>
       </c>
       <c r="D20" s="4">
-        <v>8.8745127311934971E-2</v>
+        <v>8.9382147395171543E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.4379075701729515E-2</v>
@@ -884,13 +884,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5">
-        <v>1.2418783911219233</v>
+        <v>1.2431134266853894</v>
       </c>
       <c r="C21" s="5">
         <v>1.2500987751876729</v>
       </c>
       <c r="D21" s="6">
-        <v>0.10671806472596695</v>
+        <v>0.10644726879545371</v>
       </c>
       <c r="E21" s="6">
         <v>0.10502560284352211</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2851C58-0B7B-4C09-810D-3456FBF45C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FCDE78-2AE7-4C0E-A713-00CF311DBE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4236736736736735</v>
+        <v>1.4222001982160555</v>
       </c>
       <c r="C2" s="3">
         <v>1.4056690594515</v>
       </c>
       <c r="D2" s="4">
-        <v>0.32780968006562755</v>
+        <v>0.33109105824446267</v>
       </c>
       <c r="E2" s="4">
         <v>0.13311608761699417</v>
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3907584128578605</v>
+        <v>1.3885318833415721</v>
       </c>
       <c r="C3" s="3">
         <v>1.3729456384323642</v>
       </c>
       <c r="D3" s="4">
-        <v>0.17628829466973614</v>
+        <v>0.1791216575172658</v>
       </c>
       <c r="E3" s="4">
         <v>0.17603857566765579</v>
@@ -595,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3465346534653464</v>
+        <v>1.3452464377481896</v>
       </c>
       <c r="C4" s="3">
         <v>1.3143459915611815</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2174826967444245</v>
+        <v>0.21948218405537043</v>
       </c>
       <c r="E4" s="4">
         <v>0.20968812209688123</v>
@@ -612,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2902684563758389</v>
+        <v>1.2901798063623791</v>
       </c>
       <c r="C5" s="3">
         <v>1.3254151291512914</v>
       </c>
       <c r="D5" s="4">
-        <v>8.5346062052505972E-2</v>
+        <v>8.6276849642004771E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.7558780515243554E-2</v>
@@ -629,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2657560183932917</v>
+        <v>1.2639202657807309</v>
       </c>
       <c r="C6" s="3">
         <v>1.2475728155339807</v>
       </c>
       <c r="D6" s="4">
-        <v>0.12364755263465944</v>
+        <v>0.12583822471947692</v>
       </c>
       <c r="E6" s="4">
         <v>0.13061988586611914</v>
@@ -643,36 +643,36 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2351333976213434</v>
+        <v>1.2339280221470317</v>
       </c>
       <c r="C7" s="3">
-        <v>1.2359058565955119</v>
+        <v>1.2051149127354415</v>
       </c>
       <c r="D7" s="4">
-        <v>0.112328717661714</v>
+        <v>9.9857171378987294E-2</v>
       </c>
       <c r="E7" s="4">
-        <v>0.10872087833615995</v>
+        <v>9.0552043562621268E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1.234790726622063</v>
+        <v>1.2336731443134756</v>
       </c>
       <c r="C8" s="3">
-        <v>1.2051149127354415</v>
+        <v>1.2359058565955119</v>
       </c>
       <c r="D8" s="4">
-        <v>9.8705327661142941E-2</v>
+        <v>0.11333971222761821</v>
       </c>
       <c r="E8" s="4">
-        <v>9.0552043562621268E-2</v>
+        <v>0.10872087833615995</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -680,13 +680,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2319288751449555</v>
+        <v>1.2301663161919327</v>
       </c>
       <c r="C9" s="3">
         <v>1.228626630172275</v>
       </c>
       <c r="D9" s="4">
-        <v>9.8925471301288675E-2</v>
+        <v>0.10001529578218807</v>
       </c>
       <c r="E9" s="4">
         <v>0.10461160142828269</v>
@@ -697,13 +697,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2210355987055015</v>
+        <v>1.2205835203590896</v>
       </c>
       <c r="C10" s="3">
         <v>1.2559274755927476</v>
       </c>
       <c r="D10" s="4">
-        <v>6.9622820062187368E-2</v>
+        <v>7.0276238114550943E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.5478980981121477E-2</v>
@@ -711,53 +711,53 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2116448326055314</v>
+        <v>1.2121951219512197</v>
       </c>
       <c r="C11" s="3">
-        <v>1.2169246130803795</v>
+        <v>1.3651176825588414</v>
       </c>
       <c r="D11" s="4">
-        <v>9.8644535064039973E-2</v>
+        <v>9.0368084637425614E-2</v>
       </c>
       <c r="E11" s="4">
-        <v>0.10506989797256537</v>
+        <v>8.6908633168991917E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3">
-        <v>1.211464522894093</v>
+        <v>1.2109959700633275</v>
       </c>
       <c r="C12" s="3">
-        <v>1.2094943240454077</v>
+        <v>1.2169246130803795</v>
       </c>
       <c r="D12" s="4">
-        <v>9.3402108974568243E-2</v>
+        <v>9.9764516684854407E-2</v>
       </c>
       <c r="E12" s="4">
-        <v>9.7972802183913854E-2</v>
+        <v>0.10506989797256537</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2112415071031502</v>
+        <v>1.2090784044016507</v>
       </c>
       <c r="C13" s="3">
-        <v>1.3651176825588414</v>
+        <v>1.2094943240454077</v>
       </c>
       <c r="D13" s="4">
-        <v>8.9210932334141499E-2</v>
+        <v>9.4936502236296558E-2</v>
       </c>
       <c r="E13" s="4">
-        <v>8.6908633168991917E-2</v>
+        <v>9.7972802183913854E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -765,13 +765,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="3">
-        <v>1.2000544365813826</v>
+        <v>1.2007545136081919</v>
       </c>
       <c r="C14" s="3">
         <v>1.1941026236359416</v>
       </c>
       <c r="D14" s="4">
-        <v>0.11636524878852184</v>
+        <v>0.11753713616064358</v>
       </c>
       <c r="E14" s="4">
         <v>0.10437416696958682</v>
@@ -782,13 +782,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1962369771419685</v>
+        <v>1.195474834539018</v>
       </c>
       <c r="C15" s="3">
         <v>1.2041379310344826</v>
       </c>
       <c r="D15" s="4">
-        <v>0.12587836912055433</v>
+        <v>0.12717023233964259</v>
       </c>
       <c r="E15" s="4">
         <v>0.12276275462688589</v>
@@ -799,13 +799,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1961240310077519</v>
+        <v>1.1952344350499615</v>
       </c>
       <c r="C16" s="3">
         <v>1.2434956637758505</v>
       </c>
       <c r="D16" s="4">
-        <v>8.6322269807280513E-2</v>
+        <v>8.7058351177730198E-2</v>
       </c>
       <c r="E16" s="4">
         <v>8.6527360886631266E-2</v>
@@ -816,13 +816,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1959459459459461</v>
+        <v>1.1950010773540185</v>
       </c>
       <c r="C17" s="3">
         <v>1.2261133603238867</v>
       </c>
       <c r="D17" s="4">
-        <v>8.3750136906283079E-2</v>
+        <v>8.4717607973421927E-2</v>
       </c>
       <c r="E17" s="4">
         <v>8.3798408848026321E-2</v>
@@ -833,13 +833,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1.191798514691637</v>
+        <v>1.1926634768740032</v>
       </c>
       <c r="C18" s="3">
         <v>1.2214765100671141</v>
       </c>
       <c r="D18" s="4">
-        <v>8.1840283283124565E-2</v>
+        <v>8.2844458538132229E-2</v>
       </c>
       <c r="E18" s="4">
         <v>8.3441602078759919E-2</v>
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1892171039041521</v>
+        <v>1.1886484279297673</v>
       </c>
       <c r="C19" s="3">
         <v>1.2018115942028984</v>
       </c>
       <c r="D19" s="4">
-        <v>8.8103081150927257E-2</v>
+        <v>8.914044442826724E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.8781664656212303E-2</v>
@@ -867,13 +867,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1745890715237672</v>
+        <v>1.1743159752868491</v>
       </c>
       <c r="C20" s="3">
         <v>1.2132932782576042</v>
       </c>
       <c r="D20" s="4">
-        <v>8.9382147395171543E-2</v>
+        <v>8.9977763659466331E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.4379075701729515E-2</v>
@@ -884,13 +884,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5">
-        <v>1.2431134266853894</v>
+        <v>1.2421997638847446</v>
       </c>
       <c r="C21" s="5">
         <v>1.2500987751876729</v>
       </c>
       <c r="D21" s="6">
-        <v>0.10644726879545371</v>
+        <v>0.10767939114715899</v>
       </c>
       <c r="E21" s="6">
         <v>0.10502560284352211</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FCDE78-2AE7-4C0E-A713-00CF311DBE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19031C7C-4921-443D-B2D0-6D80012A49C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -189,12 +189,8 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4222001982160555</v>
+        <v>1.4187708432586945</v>
       </c>
       <c r="C2" s="3">
         <v>1.4056690594515</v>
       </c>
       <c r="D2" s="4">
-        <v>0.33109105824446267</v>
+        <v>0.33034309096632042</v>
       </c>
       <c r="E2" s="4">
         <v>0.13311608761699417</v>
@@ -578,13 +574,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3885318833415721</v>
+        <v>1.3838432122370936</v>
       </c>
       <c r="C3" s="3">
         <v>1.3729456384323642</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1791216575172658</v>
+        <v>0.17746861214794707</v>
       </c>
       <c r="E3" s="4">
         <v>0.17603857566765579</v>
@@ -595,13 +591,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3452464377481896</v>
+        <v>1.3383475527615625</v>
       </c>
       <c r="C4" s="3">
         <v>1.3143459915611815</v>
       </c>
       <c r="D4" s="4">
-        <v>0.21948218405537043</v>
+        <v>0.22076827757125156</v>
       </c>
       <c r="E4" s="4">
         <v>0.20968812209688123</v>
@@ -612,13 +608,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2901798063623791</v>
+        <v>1.2902445579145392</v>
       </c>
       <c r="C5" s="3">
         <v>1.3254151291512914</v>
       </c>
       <c r="D5" s="4">
-        <v>8.6276849642004771E-2</v>
+        <v>8.5907558756983887E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.7558780515243554E-2</v>
@@ -629,13 +625,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2639202657807309</v>
+        <v>1.2614203454894433</v>
       </c>
       <c r="C6" s="3">
         <v>1.2475728155339807</v>
       </c>
       <c r="D6" s="4">
-        <v>0.12583822471947692</v>
+        <v>0.13068780414388201</v>
       </c>
       <c r="E6" s="4">
         <v>0.13061988586611914</v>
@@ -646,13 +642,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2339280221470317</v>
+        <v>1.2332888691270194</v>
       </c>
       <c r="C7" s="3">
         <v>1.2051149127354415</v>
       </c>
       <c r="D7" s="4">
-        <v>9.9857171378987294E-2</v>
+        <v>9.9319908143437552E-2</v>
       </c>
       <c r="E7" s="4">
         <v>9.0552043562621268E-2</v>
@@ -660,36 +656,36 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2336731443134756</v>
+        <v>1.2322222222222221</v>
       </c>
       <c r="C8" s="3">
-        <v>1.2359058565955119</v>
+        <v>1.228626630172275</v>
       </c>
       <c r="D8" s="4">
-        <v>0.11333971222761821</v>
+        <v>9.9529997235277848E-2</v>
       </c>
       <c r="E8" s="4">
-        <v>0.10872087833615995</v>
+        <v>0.10461160142828269</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2301663161919327</v>
+        <v>1.2312914673661473</v>
       </c>
       <c r="C9" s="3">
-        <v>1.228626630172275</v>
+        <v>1.2359058565955119</v>
       </c>
       <c r="D9" s="4">
-        <v>0.10001529578218807</v>
+        <v>0.11278561857195064</v>
       </c>
       <c r="E9" s="4">
-        <v>0.10461160142828269</v>
+        <v>0.10872087833615995</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -697,13 +693,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2205835203590896</v>
+        <v>1.2199001871490955</v>
       </c>
       <c r="C10" s="3">
         <v>1.2559274755927476</v>
       </c>
       <c r="D10" s="4">
-        <v>7.0276238114550943E-2</v>
+        <v>6.98216346886774E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.5478980981121477E-2</v>
@@ -711,19 +707,19 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2121951219512197</v>
+        <v>1.2095808383233533</v>
       </c>
       <c r="C11" s="3">
-        <v>1.3651176825588414</v>
+        <v>1.2094943240454077</v>
       </c>
       <c r="D11" s="4">
-        <v>9.0368084637425614E-2</v>
+        <v>9.4439208294062202E-2</v>
       </c>
       <c r="E11" s="4">
-        <v>8.6908633168991917E-2</v>
+        <v>9.7972802183913854E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -731,13 +727,13 @@
         <v>12</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2109959700633275</v>
+        <v>1.2094124199387359</v>
       </c>
       <c r="C12" s="3">
         <v>1.2169246130803795</v>
       </c>
       <c r="D12" s="4">
-        <v>9.9764516684854407E-2</v>
+        <v>9.9300389901280317E-2</v>
       </c>
       <c r="E12" s="4">
         <v>0.10506989797256537</v>
@@ -745,19 +741,19 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2090784044016507</v>
+        <v>1.2071806945261918</v>
       </c>
       <c r="C13" s="3">
-        <v>1.2094943240454077</v>
+        <v>1.3651176825588414</v>
       </c>
       <c r="D13" s="4">
-        <v>9.4936502236296558E-2</v>
+        <v>8.9694857987540913E-2</v>
       </c>
       <c r="E13" s="4">
-        <v>9.7972802183913854E-2</v>
+        <v>8.6908633168991917E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -765,13 +761,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="3">
-        <v>1.2007545136081919</v>
+        <v>1.1984251968503936</v>
       </c>
       <c r="C14" s="3">
         <v>1.1941026236359416</v>
       </c>
       <c r="D14" s="4">
-        <v>0.11753713616064358</v>
+        <v>0.11694290976058933</v>
       </c>
       <c r="E14" s="4">
         <v>0.10437416696958682</v>
@@ -779,53 +775,53 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="3">
-        <v>1.195474834539018</v>
+        <v>1.1969823973176865</v>
       </c>
       <c r="C15" s="3">
-        <v>1.2041379310344826</v>
+        <v>1.2261133603238867</v>
       </c>
       <c r="D15" s="4">
-        <v>0.12717023233964259</v>
+        <v>8.4178588438674165E-2</v>
       </c>
       <c r="E15" s="4">
-        <v>0.12276275462688589</v>
+        <v>8.3798408848026321E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1952344350499615</v>
+        <v>1.1938076808573979</v>
       </c>
       <c r="C16" s="3">
-        <v>1.2434956637758505</v>
+        <v>1.2041379310344826</v>
       </c>
       <c r="D16" s="4">
-        <v>8.7058351177730198E-2</v>
+        <v>0.12665434938350742</v>
       </c>
       <c r="E16" s="4">
-        <v>8.6527360886631266E-2</v>
+        <v>0.12276275462688589</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1950010773540185</v>
+        <v>1.19311377245509</v>
       </c>
       <c r="C17" s="3">
-        <v>1.2261133603238867</v>
+        <v>1.2434956637758505</v>
       </c>
       <c r="D17" s="4">
-        <v>8.4717607973421927E-2</v>
+        <v>8.622136172959019E-2</v>
       </c>
       <c r="E17" s="4">
-        <v>8.3798408848026321E-2</v>
+        <v>8.6527360886631266E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -833,13 +829,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1926634768740032</v>
+        <v>1.1923673596028546</v>
       </c>
       <c r="C18" s="3">
         <v>1.2214765100671141</v>
       </c>
       <c r="D18" s="4">
-        <v>8.2844458538132229E-2</v>
+        <v>8.2683427398665979E-2</v>
       </c>
       <c r="E18" s="4">
         <v>8.3441602078759919E-2</v>
@@ -850,13 +846,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1886484279297673</v>
+        <v>1.1890122967076555</v>
       </c>
       <c r="C19" s="3">
         <v>1.2018115942028984</v>
       </c>
       <c r="D19" s="4">
-        <v>8.914044442826724E-2</v>
+        <v>8.8524475033359085E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.8781664656212303E-2</v>
@@ -867,13 +863,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1743159752868491</v>
+        <v>1.1725321888412017</v>
       </c>
       <c r="C20" s="3">
         <v>1.2132932782576042</v>
       </c>
       <c r="D20" s="4">
-        <v>8.9977763659466331E-2</v>
+        <v>8.9405625263804148E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.4379075701729515E-2</v>
@@ -884,16 +880,20 @@
         <v>20</v>
       </c>
       <c r="B21" s="5">
-        <v>1.2421997638847446</v>
+        <f>AVERAGE(B2:B20)</f>
+        <v>1.2406181106813883</v>
       </c>
       <c r="C21" s="5">
-        <v>1.2500987751876729</v>
+        <f>AVERAGE(C2:C20)</f>
+        <v>1.2572363731688787</v>
       </c>
       <c r="D21" s="6">
-        <v>0.10767939114715899</v>
+        <f>AVERAGE(D2:D20)</f>
+        <v>0.12024619449562117</v>
       </c>
       <c r="E21" s="6">
-        <v>0.10502560284352211</v>
+        <f>AVERAGE(E2:E20)</f>
+        <v>0.10949480648233589</v>
       </c>
     </row>
   </sheetData>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor_Occidente\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19031C7C-4921-443D-B2D0-6D80012A49C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6968C8-9982-4055-9939-9BE99BBF7149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,9 +129,9 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -177,11 +177,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -189,8 +186,15 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,347 +557,343 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>1.4187708432586945</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1.4056690594515</v>
-      </c>
-      <c r="D2" s="4">
-        <v>0.33034309096632042</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0.13311608761699417</v>
+      <c r="B2" s="4">
+        <v>1.4144676979071884</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.4160828025477705</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.33539330128938732</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.13068903086175682</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
-        <v>1.3838432122370936</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1.3729456384323642</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.17746861214794707</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.17603857566765579</v>
+      <c r="B3" s="4">
+        <v>1.37693710118505</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.3706164636397193</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.18011657499384287</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.17533980582524272</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
-        <v>1.3383475527615625</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1.3143459915611815</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.22076827757125156</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.20968812209688123</v>
+      <c r="B4" s="4">
+        <v>1.3332619863013699</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.3269511305616337</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0.22367980083305405</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.20836657927732816</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
-        <v>1.2902445579145392</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1.3254151291512914</v>
-      </c>
-      <c r="D5" s="4">
-        <v>8.5907558756983887E-2</v>
-      </c>
-      <c r="E5" s="4">
-        <v>9.7558780515243554E-2</v>
+      <c r="B5" s="4">
+        <v>1.2903225806451613</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.3297448165869219</v>
+      </c>
+      <c r="D5" s="5">
+        <v>8.6710376155205979E-2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>9.792093704245973E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>1.2614203454894433</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1.2475728155339807</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.13068780414388201</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.13061988586611914</v>
+      <c r="B6" s="4">
+        <v>1.2570601013758145</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1.2581814618851657</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0.13856419003662268</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.13729552303056392</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.2311637778563849</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.2293759728314702</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.1007501915572266</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.1025868075717106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3">
-        <v>1.2332888691270194</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1.2051149127354415</v>
-      </c>
-      <c r="D7" s="4">
-        <v>9.9319908143437552E-2</v>
-      </c>
-      <c r="E7" s="4">
-        <v>9.0552043562621268E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1.2322222222222221</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1.228626630172275</v>
-      </c>
-      <c r="D8" s="4">
-        <v>9.9529997235277848E-2</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.10461160142828269</v>
+      <c r="B8" s="4">
+        <v>1.230747491875088</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.2054814597684305</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.10082058295580819</v>
+      </c>
+      <c r="E8" s="5">
+        <v>8.9561838754561446E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="3">
-        <v>1.2312914673661473</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1.2359058565955119</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.11278561857195064</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.10872087833615995</v>
+      <c r="B9" s="4">
+        <v>1.2289952996474738</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1.2420450482659993</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.1146012187321146</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.10830031363337163</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
-        <v>1.2199001871490955</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1.2559274755927476</v>
-      </c>
-      <c r="D10" s="4">
-        <v>6.98216346886774E-2</v>
-      </c>
-      <c r="E10" s="4">
-        <v>7.5478980981121477E-2</v>
+      <c r="B10" s="4">
+        <v>1.2212230215827338</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1.2619678142187818</v>
+      </c>
+      <c r="D10" s="5">
+        <v>7.054793072091696E-2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>7.4387804582373623E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
-        <v>1.2095808383233533</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1.2094943240454077</v>
-      </c>
-      <c r="D11" s="4">
-        <v>9.4439208294062202E-2</v>
-      </c>
-      <c r="E11" s="4">
-        <v>9.7972802183913854E-2</v>
+      <c r="B11" s="4">
+        <v>1.2106598984771575</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1.2084191260581101</v>
+      </c>
+      <c r="D11" s="5">
+        <v>9.593085187326901E-2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>9.5474203835568566E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3">
-        <v>1.2094124199387359</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1.2169246130803795</v>
-      </c>
-      <c r="D12" s="4">
-        <v>9.9300389901280317E-2</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0.10506989797256537</v>
+      <c r="B12" s="4">
+        <v>1.2065765049058603</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1.2147368421052631</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.10051979208316673</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.10502111477149616</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
-        <v>1.2071806945261918</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1.3651176825588414</v>
-      </c>
-      <c r="D13" s="4">
-        <v>8.9694857987540913E-2</v>
-      </c>
-      <c r="E13" s="4">
-        <v>8.6908633168991917E-2</v>
+      <c r="B13" s="4">
+        <v>1.2061328790459964</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1.3511652542372883</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9.0219785849684916E-2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>8.5160126296797478E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="3">
-        <v>1.1984251968503936</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1.1941026236359416</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0.11694290976058933</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0.10437416696958682</v>
+      <c r="B14" s="4">
+        <v>1.1964735516372795</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1.1943195749897833</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.11809501145253889</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.10163859525243504</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="3">
-        <v>1.1969823973176865</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1.2261133603238867</v>
-      </c>
-      <c r="D15" s="4">
-        <v>8.4178588438674165E-2</v>
-      </c>
-      <c r="E15" s="4">
-        <v>8.3798408848026321E-2</v>
+      <c r="B15" s="4">
+        <v>1.1954947707160095</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1.229799723756906</v>
+      </c>
+      <c r="D15" s="5">
+        <v>8.5288870591464255E-2</v>
+      </c>
+      <c r="E15" s="5">
+        <v>8.3542478003750184E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1.1942296252230813</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1.2209902011346054</v>
+      </c>
+      <c r="D16" s="5">
+        <v>8.3698466440948013E-2</v>
+      </c>
+      <c r="E16" s="5">
+        <v>8.3078043659889883E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="3">
-        <v>1.1938076808573979</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1.2041379310344826</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0.12665434938350742</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0.12276275462688589</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="B17" s="4">
+        <v>1.1928703309189035</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1.201057565196491</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.12874147483132509</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.12090083545223393</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="3">
-        <v>1.19311377245509</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1.2434956637758505</v>
-      </c>
-      <c r="D17" s="4">
-        <v>8.622136172959019E-2</v>
-      </c>
-      <c r="E17" s="4">
-        <v>8.6527360886631266E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3">
-        <v>1.1923673596028546</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1.2214765100671141</v>
-      </c>
-      <c r="D18" s="4">
-        <v>8.2683427398665979E-2</v>
-      </c>
-      <c r="E18" s="4">
-        <v>8.3441602078759919E-2</v>
+      <c r="B18" s="4">
+        <v>1.1920863309352521</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1.2427643236857648</v>
+      </c>
+      <c r="D18" s="5">
+        <v>8.7158264359167292E-2</v>
+      </c>
+      <c r="E18" s="5">
+        <v>8.3460685235395612E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
-        <v>1.1890122967076555</v>
-      </c>
-      <c r="C19" s="3">
-        <v>1.2018115942028984</v>
-      </c>
-      <c r="D19" s="4">
-        <v>8.8524475033359085E-2</v>
-      </c>
-      <c r="E19" s="4">
-        <v>8.8781664656212303E-2</v>
+      <c r="B19" s="4">
+        <v>1.1891943127962084</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1.2040006350214318</v>
+      </c>
+      <c r="D19" s="5">
+        <v>8.9587473038841056E-2</v>
+      </c>
+      <c r="E19" s="5">
+        <v>8.6923522755499125E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
-        <v>1.1725321888412017</v>
-      </c>
-      <c r="C20" s="3">
-        <v>1.2132932782576042</v>
-      </c>
-      <c r="D20" s="4">
-        <v>8.9405625263804148E-2</v>
-      </c>
-      <c r="E20" s="4">
-        <v>9.4379075701729515E-2</v>
+      <c r="B20" s="4">
+        <v>1.1712046204620461</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1.2093946410850147</v>
+      </c>
+      <c r="D20" s="5">
+        <v>9.030960098356991E-2</v>
+      </c>
+      <c r="E20" s="5">
+        <v>9.2698782619361569E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5">
-        <f>AVERAGE(B2:B20)</f>
-        <v>1.2406181106813883</v>
-      </c>
-      <c r="C21" s="5">
-        <f>AVERAGE(C2:C20)</f>
-        <v>1.2572363731688787</v>
-      </c>
-      <c r="D21" s="6">
-        <f>AVERAGE(D2:D20)</f>
-        <v>0.12024619449562117</v>
-      </c>
-      <c r="E21" s="6">
-        <f>AVERAGE(E2:E20)</f>
-        <v>0.10949480648233589</v>
+      <c r="B21" s="7">
+        <v>1.2391267862280619</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1.2531976344381792</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.10946952895136758</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.10435572432062265</v>
       </c>
     </row>
   </sheetData>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6968C8-9982-4055-9939-9BE99BBF7149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D932E970-CA94-425B-8668-5D4D2D9A3E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,17 +177,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -195,6 +189,8 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,342 +553,342 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>1.4144676979071884</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2" s="3">
+        <v>1.4125390450691657</v>
+      </c>
+      <c r="C2" s="3">
         <v>1.4160828025477705</v>
       </c>
-      <c r="D2" s="5">
-        <v>0.33539330128938732</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="4">
+        <v>0.33165606038182627</v>
+      </c>
+      <c r="E2" s="4">
         <v>0.13068903086175682</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
-        <v>1.37693710118505</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="3">
+        <v>1.3772401433691757</v>
+      </c>
+      <c r="C3" s="3">
         <v>1.3706164636397193</v>
       </c>
-      <c r="D3" s="5">
-        <v>0.18011657499384287</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3" s="4">
+        <v>0.17602523659305994</v>
+      </c>
+      <c r="E3" s="4">
         <v>0.17533980582524272</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>1.3332619863013699</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="3">
+        <v>1.3329103214890017</v>
+      </c>
+      <c r="C4" s="3">
         <v>1.3269511305616337</v>
       </c>
-      <c r="D4" s="5">
-        <v>0.22367980083305405</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="4">
+        <v>0.21927464984695297</v>
+      </c>
+      <c r="E4" s="4">
         <v>0.20836657927732816</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>1.2903225806451613</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="B5" s="3">
+        <v>1.2918891431477244</v>
+      </c>
+      <c r="C5" s="3">
         <v>1.3297448165869219</v>
       </c>
-      <c r="D5" s="5">
-        <v>8.6710376155205979E-2</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="4">
+        <v>8.5144613785936962E-2</v>
+      </c>
+      <c r="E5" s="4">
         <v>9.792093704245973E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>1.2570601013758145</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="B6" s="3">
+        <v>1.2556791292001892</v>
+      </c>
+      <c r="C6" s="3">
         <v>1.2581814618851657</v>
       </c>
-      <c r="D6" s="5">
-        <v>0.13856419003662268</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6" s="4">
+        <v>0.14134015618990284</v>
+      </c>
+      <c r="E6" s="4">
         <v>0.13729552303056392</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4">
-        <v>1.2311637778563849</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="3">
+        <v>1.2306620209059234</v>
+      </c>
+      <c r="C7" s="3">
         <v>1.2293759728314702</v>
       </c>
-      <c r="D7" s="5">
-        <v>0.1007501915572266</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" s="4">
+        <v>9.8512022242435687E-2</v>
+      </c>
+      <c r="E7" s="4">
         <v>0.1025868075717106</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
-        <v>1.230747491875088</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="B8" s="3">
+        <v>1.2295127353266886</v>
+      </c>
+      <c r="C8" s="3">
         <v>1.2054814597684305</v>
       </c>
-      <c r="D8" s="5">
-        <v>0.10082058295580819</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="4">
+        <v>9.9041664952905853E-2</v>
+      </c>
+      <c r="E8" s="4">
         <v>8.9561838754561446E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="4">
-        <v>1.2289952996474738</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="B9" s="3">
+        <v>1.2288111078970205</v>
+      </c>
+      <c r="C9" s="3">
         <v>1.2420450482659993</v>
       </c>
-      <c r="D9" s="5">
-        <v>0.1146012187321146</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" s="4">
+        <v>0.11215468717050303</v>
+      </c>
+      <c r="E9" s="4">
         <v>0.10830031363337163</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
-        <v>1.2212230215827338</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="B10" s="3">
+        <v>1.2204491725768321</v>
+      </c>
+      <c r="C10" s="3">
         <v>1.2619678142187818</v>
       </c>
-      <c r="D10" s="5">
-        <v>7.054793072091696E-2</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="4">
+        <v>6.9208115183246072E-2</v>
+      </c>
+      <c r="E10" s="4">
         <v>7.4387804582373623E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
-        <v>1.2106598984771575</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="B11" s="3">
+        <v>1.2112983770287142</v>
+      </c>
+      <c r="C11" s="3">
         <v>1.2084191260581101</v>
       </c>
-      <c r="D11" s="5">
-        <v>9.593085187326901E-2</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="4">
+        <v>9.4171589806895342E-2</v>
+      </c>
+      <c r="E11" s="4">
         <v>9.5474203835568566E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.2066069428891377</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1.3511652542372883</v>
+      </c>
+      <c r="D12" s="4">
+        <v>8.809312419848081E-2</v>
+      </c>
+      <c r="E12" s="4">
+        <v>8.5160126296797478E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4">
-        <v>1.2065765049058603</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="B13" s="3">
+        <v>1.2062710546773776</v>
+      </c>
+      <c r="C13" s="3">
         <v>1.2147368421052631</v>
       </c>
-      <c r="D12" s="5">
-        <v>0.10051979208316673</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D13" s="4">
+        <v>9.8758797184900826E-2</v>
+      </c>
+      <c r="E13" s="4">
         <v>0.10502111477149616</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4">
-        <v>1.2061328790459964</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1.3511652542372883</v>
-      </c>
-      <c r="D13" s="5">
-        <v>9.0219785849684916E-2</v>
-      </c>
-      <c r="E13" s="5">
-        <v>8.5160126296797478E-2</v>
-      </c>
-    </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="4">
-        <v>1.1964735516372795</v>
-      </c>
-      <c r="C14" s="4">
+      <c r="B14" s="3">
+        <v>1.1960735586481113</v>
+      </c>
+      <c r="C14" s="3">
         <v>1.1943195749897833</v>
       </c>
-      <c r="D14" s="5">
-        <v>0.11809501145253889</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="D14" s="4">
+        <v>0.11561557247521907</v>
+      </c>
+      <c r="E14" s="4">
         <v>0.10163859525243504</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="4">
-        <v>1.1954947707160095</v>
-      </c>
-      <c r="C15" s="4">
+      <c r="B15" s="3">
+        <v>1.1949337027508411</v>
+      </c>
+      <c r="C15" s="3">
         <v>1.229799723756906</v>
       </c>
-      <c r="D15" s="5">
-        <v>8.5288870591464255E-2</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="D15" s="4">
+        <v>8.3650630732046483E-2</v>
+      </c>
+      <c r="E15" s="4">
         <v>8.3542478003750184E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1.1948972360028349</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1.2427643236857648</v>
+      </c>
+      <c r="D16" s="4">
+        <v>8.5040983606557374E-2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>8.3460685235395612E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="4">
-        <v>1.1942296252230813</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="B17" s="3">
+        <v>1.1948732886688027</v>
+      </c>
+      <c r="C17" s="3">
         <v>1.2209902011346054</v>
       </c>
-      <c r="D16" s="5">
-        <v>8.3698466440948013E-2</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="D17" s="4">
+        <v>8.2502222969887767E-2</v>
+      </c>
+      <c r="E17" s="4">
         <v>8.3078043659889883E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="4">
-        <v>1.1928703309189035</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B18" s="3">
+        <v>1.1919742729306486</v>
+      </c>
+      <c r="C18" s="3">
         <v>1.201057565196491</v>
       </c>
-      <c r="D17" s="5">
-        <v>0.12874147483132509</v>
-      </c>
-      <c r="E17" s="5">
+      <c r="D18" s="4">
+        <v>0.12587781825861977</v>
+      </c>
+      <c r="E18" s="4">
         <v>0.12090083545223393</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="4">
-        <v>1.1920863309352521</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1.2427643236857648</v>
-      </c>
-      <c r="D18" s="5">
-        <v>8.7158264359167292E-2</v>
-      </c>
-      <c r="E18" s="5">
-        <v>8.3460685235395612E-2</v>
-      </c>
-    </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4">
-        <v>1.1891943127962084</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="B19" s="3">
+        <v>1.188749766398804</v>
+      </c>
+      <c r="C19" s="3">
         <v>1.2040006350214318</v>
       </c>
-      <c r="D19" s="5">
-        <v>8.9587473038841056E-2</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" s="4">
+        <v>8.7794713613020728E-2</v>
+      </c>
+      <c r="E19" s="4">
         <v>8.6923522755499125E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4">
-        <v>1.1712046204620461</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="B20" s="3">
+        <v>1.1698496546119463</v>
+      </c>
+      <c r="C20" s="3">
         <v>1.2093946410850147</v>
       </c>
-      <c r="D20" s="5">
-        <v>9.030960098356991E-2</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D20" s="4">
+        <v>8.8483802538381326E-2</v>
+      </c>
+      <c r="E20" s="4">
         <v>9.2698782619361569E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="7">
-        <v>1.2391267862280619</v>
-      </c>
-      <c r="C21" s="7">
+      <c r="B21" s="5">
+        <v>1.2386734729967108</v>
+      </c>
+      <c r="C21" s="5">
         <v>1.2531976344381792</v>
       </c>
-      <c r="D21" s="8">
-        <v>0.10946952895136758</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="D21" s="6">
+        <v>0.10766239222400906</v>
+      </c>
+      <c r="E21" s="6">
         <v>0.10435572432062265</v>
       </c>
     </row>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D932E970-CA94-425B-8668-5D4D2D9A3E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D1AB9B-A548-44AE-B40F-274C0DA152F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -189,8 +189,12 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4125390450691657</v>
+        <v>1.4130002210921955</v>
       </c>
       <c r="C2" s="3">
         <v>1.4160828025477705</v>
       </c>
       <c r="D2" s="4">
-        <v>0.33165606038182627</v>
+        <v>0.3346899511617582</v>
       </c>
       <c r="E2" s="4">
         <v>0.13068903086175682</v>
@@ -574,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3772401433691757</v>
+        <v>1.3753887161261662</v>
       </c>
       <c r="C3" s="3">
         <v>1.3706164636397193</v>
       </c>
       <c r="D3" s="4">
-        <v>0.17602523659305994</v>
+        <v>0.1775236593059937</v>
       </c>
       <c r="E3" s="4">
         <v>0.17533980582524272</v>
@@ -591,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3329103214890017</v>
+        <v>1.3332632906072703</v>
       </c>
       <c r="C4" s="3">
         <v>1.3269511305616337</v>
       </c>
       <c r="D4" s="4">
-        <v>0.21927464984695297</v>
+        <v>0.22071236434468045</v>
       </c>
       <c r="E4" s="4">
         <v>0.20836657927732816</v>
@@ -608,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2918891431477244</v>
+        <v>1.2915297092288243</v>
       </c>
       <c r="C5" s="3">
         <v>1.3297448165869219</v>
       </c>
       <c r="D5" s="4">
-        <v>8.5144613785936962E-2</v>
+        <v>8.5620886733633536E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.792093704245973E-2</v>
@@ -625,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2556791292001892</v>
+        <v>1.2548674642270701</v>
       </c>
       <c r="C6" s="3">
         <v>1.2581814618851657</v>
       </c>
       <c r="D6" s="4">
-        <v>0.14134015618990284</v>
+        <v>0.14257763507750965</v>
       </c>
       <c r="E6" s="4">
         <v>0.13729552303056392</v>
@@ -642,13 +646,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2306620209059234</v>
+        <v>1.230689476412649</v>
       </c>
       <c r="C7" s="3">
         <v>1.2293759728314702</v>
       </c>
       <c r="D7" s="4">
-        <v>9.8512022242435687E-2</v>
+        <v>9.9318653783445177E-2</v>
       </c>
       <c r="E7" s="4">
         <v>0.1025868075717106</v>
@@ -656,36 +660,36 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2295127353266886</v>
+        <v>1.2289243142323711</v>
       </c>
       <c r="C8" s="3">
-        <v>1.2054814597684305</v>
+        <v>1.2420450482659993</v>
       </c>
       <c r="D8" s="4">
-        <v>9.9041664952905853E-2</v>
+        <v>0.11294953525719013</v>
       </c>
       <c r="E8" s="4">
-        <v>8.9561838754561446E-2</v>
+        <v>0.10830031363337163</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2288111078970205</v>
+        <v>1.2288147232523006</v>
       </c>
       <c r="C9" s="3">
-        <v>1.2420450482659993</v>
+        <v>1.2054814597684305</v>
       </c>
       <c r="D9" s="4">
-        <v>0.11215468717050303</v>
+        <v>9.9823139884012674E-2</v>
       </c>
       <c r="E9" s="4">
-        <v>0.10830031363337163</v>
+        <v>8.9561838754561446E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -693,13 +697,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2204491725768321</v>
+        <v>1.2197769953051645</v>
       </c>
       <c r="C10" s="3">
         <v>1.2619678142187818</v>
       </c>
       <c r="D10" s="4">
-        <v>6.9208115183246072E-2</v>
+        <v>6.9698952879581152E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.4387804582373623E-2</v>
@@ -710,13 +714,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2112983770287142</v>
+        <v>1.2115861214374224</v>
       </c>
       <c r="C11" s="3">
         <v>1.2084191260581101</v>
       </c>
       <c r="D11" s="4">
-        <v>9.4171589806895342E-2</v>
+        <v>9.4876994973988188E-2</v>
       </c>
       <c r="E11" s="4">
         <v>9.5474203835568566E-2</v>
@@ -727,13 +731,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2066069428891377</v>
+        <v>1.2061111111111109</v>
       </c>
       <c r="C12" s="3">
         <v>1.3511652542372883</v>
       </c>
       <c r="D12" s="4">
-        <v>8.809312419848081E-2</v>
+        <v>8.8783663805859725E-2</v>
       </c>
       <c r="E12" s="4">
         <v>8.5160126296797478E-2</v>
@@ -744,13 +748,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2062710546773776</v>
+        <v>1.2048717948717949</v>
       </c>
       <c r="C13" s="3">
         <v>1.2147368421052631</v>
       </c>
       <c r="D13" s="4">
-        <v>9.8758797184900826E-2</v>
+        <v>9.9808061420345484E-2</v>
       </c>
       <c r="E13" s="4">
         <v>0.10502111477149616</v>
@@ -758,36 +762,36 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3">
-        <v>1.1960735586481113</v>
+        <v>1.1954045561665356</v>
       </c>
       <c r="C14" s="3">
-        <v>1.1943195749897833</v>
+        <v>1.229799723756906</v>
       </c>
       <c r="D14" s="4">
-        <v>0.11561557247521907</v>
+        <v>8.429626196073238E-2</v>
       </c>
       <c r="E14" s="4">
-        <v>0.10163859525243504</v>
+        <v>8.3542478003750184E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1949337027508411</v>
+        <v>1.1952721004678653</v>
       </c>
       <c r="C15" s="3">
-        <v>1.229799723756906</v>
+        <v>1.1943195749897833</v>
       </c>
       <c r="D15" s="4">
-        <v>8.3650630732046483E-2</v>
+        <v>0.11667863812670594</v>
       </c>
       <c r="E15" s="4">
-        <v>8.3542478003750184E-2</v>
+        <v>0.10163859525243504</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -795,13 +799,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1948972360028349</v>
+        <v>1.1947960618846694</v>
       </c>
       <c r="C16" s="3">
         <v>1.2427643236857648</v>
       </c>
       <c r="D16" s="4">
-        <v>8.5040983606557374E-2</v>
+        <v>8.5703953712632591E-2</v>
       </c>
       <c r="E16" s="4">
         <v>8.3460685235395612E-2</v>
@@ -812,13 +816,13 @@
         <v>17</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1948732886688027</v>
+        <v>1.1945727482678983</v>
       </c>
       <c r="C17" s="3">
         <v>1.2209902011346054</v>
       </c>
       <c r="D17" s="4">
-        <v>8.2502222969887767E-2</v>
+        <v>8.3247218283626925E-2</v>
       </c>
       <c r="E17" s="4">
         <v>8.3078043659889883E-2</v>
@@ -829,13 +833,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1919742729306486</v>
+        <v>1.1928313420394554</v>
       </c>
       <c r="C18" s="3">
         <v>1.201057565196491</v>
       </c>
       <c r="D18" s="4">
-        <v>0.12587781825861977</v>
+        <v>0.12668743509865005</v>
       </c>
       <c r="E18" s="4">
         <v>0.12090083545223393</v>
@@ -846,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.188749766398804</v>
+        <v>1.1887982195845697</v>
       </c>
       <c r="C19" s="3">
         <v>1.2040006350214318</v>
       </c>
       <c r="D19" s="4">
-        <v>8.7794713613020728E-2</v>
+        <v>8.8467407176491819E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.6923522755499125E-2</v>
@@ -863,13 +867,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1698496546119463</v>
+        <v>1.1692307692307693</v>
       </c>
       <c r="C20" s="3">
         <v>1.2093946410850147</v>
       </c>
       <c r="D20" s="4">
-        <v>8.8483802538381326E-2</v>
+        <v>8.8807392226656595E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.2698782619361569E-2</v>
@@ -880,13 +884,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5">
-        <v>1.2386734729967108</v>
+        <v>1.2384768366869443</v>
       </c>
       <c r="C21" s="5">
         <v>1.2531976344381792</v>
       </c>
       <c r="D21" s="6">
-        <v>0.10766239222400906</v>
+        <v>0.10849629566636755</v>
       </c>
       <c r="E21" s="6">
         <v>0.10435572432062265</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D1AB9B-A548-44AE-B40F-274C0DA152F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD3EF82-86A4-472E-8B11-98AC8AA13536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4130002210921955</v>
+        <v>1.413394415357766</v>
       </c>
       <c r="C2" s="3">
         <v>1.4160828025477705</v>
       </c>
       <c r="D2" s="4">
-        <v>0.3346899511617582</v>
+        <v>0.33920378866360812</v>
       </c>
       <c r="E2" s="4">
         <v>0.13068903086175682</v>
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3753887161261662</v>
+        <v>1.3754940711462451</v>
       </c>
       <c r="C3" s="3">
         <v>1.3706164636397193</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1775236593059937</v>
+        <v>0.17957413249211357</v>
       </c>
       <c r="E3" s="4">
         <v>0.17533980582524272</v>
@@ -595,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3332632906072703</v>
+        <v>1.3324341149616101</v>
       </c>
       <c r="C4" s="3">
         <v>1.3269511305616337</v>
       </c>
       <c r="D4" s="4">
-        <v>0.22071236434468045</v>
+        <v>0.22349503756608849</v>
       </c>
       <c r="E4" s="4">
         <v>0.20836657927732816</v>
@@ -612,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2915297092288243</v>
+        <v>1.2917187890918187</v>
       </c>
       <c r="C5" s="3">
         <v>1.3297448165869219</v>
       </c>
       <c r="D5" s="4">
-        <v>8.5620886733633536E-2</v>
+        <v>8.6530135088326979E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.792093704245973E-2</v>
@@ -629,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2548674642270701</v>
+        <v>1.2536106296938185</v>
       </c>
       <c r="C6" s="3">
         <v>1.2581814618851657</v>
       </c>
       <c r="D6" s="4">
-        <v>0.14257763507750965</v>
+        <v>0.14473486178698641</v>
       </c>
       <c r="E6" s="4">
         <v>0.13729552303056392</v>
@@ -646,13 +646,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.230689476412649</v>
+        <v>1.2310696095076401</v>
       </c>
       <c r="C7" s="3">
         <v>1.2293759728314702</v>
       </c>
       <c r="D7" s="4">
-        <v>9.9318653783445177E-2</v>
+        <v>0.10108637822438087</v>
       </c>
       <c r="E7" s="4">
         <v>0.1025868075717106</v>
@@ -660,36 +660,36 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2289243142323711</v>
+        <v>1.2290117615249427</v>
       </c>
       <c r="C8" s="3">
-        <v>1.2420450482659993</v>
+        <v>1.2054814597684305</v>
       </c>
       <c r="D8" s="4">
-        <v>0.11294953525719013</v>
+        <v>0.10141350991924759</v>
       </c>
       <c r="E8" s="4">
-        <v>0.10830031363337163</v>
+        <v>8.9561838754561446E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2288147232523006</v>
+        <v>1.227792684649061</v>
       </c>
       <c r="C9" s="3">
-        <v>1.2054814597684305</v>
+        <v>1.2420450482659993</v>
       </c>
       <c r="D9" s="4">
-        <v>9.9823139884012674E-2</v>
+        <v>0.11486365922104888</v>
       </c>
       <c r="E9" s="4">
-        <v>8.9561838754561446E-2</v>
+        <v>0.10830031363337163</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -697,13 +697,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2197769953051645</v>
+        <v>1.2216122507945681</v>
       </c>
       <c r="C10" s="3">
         <v>1.2619678142187818</v>
       </c>
       <c r="D10" s="4">
-        <v>6.9698952879581152E-2</v>
+        <v>7.0782886125654448E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.4387804582373623E-2</v>
@@ -714,13 +714,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2115861214374224</v>
+        <v>1.2122137404580153</v>
       </c>
       <c r="C11" s="3">
         <v>1.2084191260581101</v>
       </c>
       <c r="D11" s="4">
-        <v>9.4876994973988188E-2</v>
+        <v>9.6258413426211678E-2</v>
       </c>
       <c r="E11" s="4">
         <v>9.5474203835568566E-2</v>
@@ -731,13 +731,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2061111111111109</v>
+        <v>1.2059145673603506</v>
       </c>
       <c r="C12" s="3">
         <v>1.3511652542372883</v>
       </c>
       <c r="D12" s="4">
-        <v>8.8783663805859725E-2</v>
+        <v>9.0066094505277694E-2</v>
       </c>
       <c r="E12" s="4">
         <v>8.5160126296797478E-2</v>
@@ -748,13 +748,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2048717948717949</v>
+        <v>1.2039274924471299</v>
       </c>
       <c r="C13" s="3">
         <v>1.2147368421052631</v>
       </c>
       <c r="D13" s="4">
-        <v>9.9808061420345484E-2</v>
+        <v>0.10165067178502879</v>
       </c>
       <c r="E13" s="4">
         <v>0.10502111477149616</v>
@@ -762,70 +762,70 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3">
-        <v>1.1954045561665356</v>
+        <v>1.1953771289537711</v>
       </c>
       <c r="C14" s="3">
-        <v>1.229799723756906</v>
+        <v>1.1943195749897833</v>
       </c>
       <c r="D14" s="4">
-        <v>8.429626196073238E-2</v>
+        <v>0.11808648182732366</v>
       </c>
       <c r="E14" s="4">
-        <v>8.3542478003750184E-2</v>
+        <v>0.10163859525243504</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1952721004678653</v>
+        <v>1.1951975213013168</v>
       </c>
       <c r="C15" s="3">
-        <v>1.1943195749897833</v>
+        <v>1.229799723756906</v>
       </c>
       <c r="D15" s="4">
-        <v>0.11667863812670594</v>
+        <v>8.5488196536767869E-2</v>
       </c>
       <c r="E15" s="4">
-        <v>0.10163859525243504</v>
+        <v>8.3542478003750184E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1947960618846694</v>
+        <v>1.1949417448138677</v>
       </c>
       <c r="C16" s="3">
-        <v>1.2427643236857648</v>
+        <v>1.2209902011346054</v>
       </c>
       <c r="D16" s="4">
-        <v>8.5703953712632591E-2</v>
+        <v>8.456898416284156E-2</v>
       </c>
       <c r="E16" s="4">
-        <v>8.3460685235395612E-2</v>
+        <v>8.3078043659889883E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1945727482678983</v>
+        <v>1.1933701657458562</v>
       </c>
       <c r="C17" s="3">
-        <v>1.2209902011346054</v>
+        <v>1.2427643236857648</v>
       </c>
       <c r="D17" s="4">
-        <v>8.3247218283626925E-2</v>
+        <v>8.7270973963355827E-2</v>
       </c>
       <c r="E17" s="4">
-        <v>8.3078043659889883E-2</v>
+        <v>8.3460685235395612E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -833,13 +833,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1928313420394554</v>
+        <v>1.1909451511421145</v>
       </c>
       <c r="C18" s="3">
         <v>1.201057565196491</v>
       </c>
       <c r="D18" s="4">
-        <v>0.12668743509865005</v>
+        <v>0.1286762764665505</v>
       </c>
       <c r="E18" s="4">
         <v>0.12090083545223393</v>
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1887982195845697</v>
+        <v>1.1884270280168467</v>
       </c>
       <c r="C19" s="3">
         <v>1.2040006350214318</v>
       </c>
       <c r="D19" s="4">
-        <v>8.8467407176491819E-2</v>
+        <v>8.9599501222333428E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.6923522755499125E-2</v>
@@ -867,13 +867,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1692307692307693</v>
+        <v>1.1674641148325358</v>
       </c>
       <c r="C20" s="3">
         <v>1.2093946410850147</v>
       </c>
       <c r="D20" s="4">
-        <v>8.8807392226656595E-2</v>
+        <v>9.0173659799374389E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.2698782619361569E-2</v>
@@ -884,13 +884,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5">
-        <v>1.2384768366869443</v>
+        <v>1.238038153420552</v>
       </c>
       <c r="C21" s="5">
         <v>1.2531976344381792</v>
       </c>
       <c r="D21" s="6">
-        <v>0.10849629566636755</v>
+        <v>0.11011460143350159</v>
       </c>
       <c r="E21" s="6">
         <v>0.10435572432062265</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD3EF82-86A4-472E-8B11-98AC8AA13536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1B5F61-7844-4BDC-BF71-A14AB9A88F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,9 +129,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -177,23 +177,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,342 +553,342 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>1.413394415357766</v>
-      </c>
-      <c r="C2" s="3">
+      <c r="B2" s="4">
+        <v>1.412640207075065</v>
+      </c>
+      <c r="C2" s="4">
         <v>1.4160828025477705</v>
       </c>
-      <c r="D2" s="4">
-        <v>0.33920378866360812</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="5">
+        <v>0.33149803360743652</v>
+      </c>
+      <c r="E2" s="5">
         <v>0.13068903086175682</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
-        <v>1.3754940711462451</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="B3" s="4">
+        <v>1.3764705882352943</v>
+      </c>
+      <c r="C3" s="4">
         <v>1.3706164636397193</v>
       </c>
-      <c r="D3" s="4">
-        <v>0.17957413249211357</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3" s="5">
+        <v>0.17625374395207741</v>
+      </c>
+      <c r="E3" s="5">
         <v>0.17533980582524272</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
-        <v>1.3324341149616101</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4" s="4">
+        <v>1.3320288362512873</v>
+      </c>
+      <c r="C4" s="4">
         <v>1.3269511305616337</v>
       </c>
-      <c r="D4" s="4">
-        <v>0.22349503756608849</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="5">
+        <v>0.2185165181384463</v>
+      </c>
+      <c r="E4" s="5">
         <v>0.20836657927732816</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
-        <v>1.2917187890918187</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="4">
+        <v>1.2921098194410092</v>
+      </c>
+      <c r="C5" s="4">
         <v>1.3297448165869219</v>
       </c>
-      <c r="D5" s="4">
-        <v>8.6530135088326979E-2</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="5">
+        <v>8.4702086650465094E-2</v>
+      </c>
+      <c r="E5" s="5">
         <v>9.792093704245973E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>1.2536106296938185</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="4">
+        <v>1.2546975252062329</v>
+      </c>
+      <c r="C6" s="4">
         <v>1.2581814618851657</v>
       </c>
-      <c r="D6" s="4">
-        <v>0.14473486178698641</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="5">
+        <v>0.14595561798692286</v>
+      </c>
+      <c r="E6" s="5">
         <v>0.13729552303056392</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3">
-        <v>1.2310696095076401</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" s="4">
+        <v>1.2306009089378891</v>
+      </c>
+      <c r="C7" s="4">
         <v>1.2293759728314702</v>
       </c>
-      <c r="D7" s="4">
-        <v>0.10108637822438087</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="5">
+        <v>9.8447313039587717E-2</v>
+      </c>
+      <c r="E7" s="5">
         <v>0.1025868075717106</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
-        <v>1.2290117615249427</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="4">
+        <v>1.2297604710290377</v>
+      </c>
+      <c r="C8" s="4">
         <v>1.2054814597684305</v>
       </c>
-      <c r="D8" s="4">
-        <v>0.10141350991924759</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="5">
+        <v>9.9095634647005784E-2</v>
+      </c>
+      <c r="E8" s="5">
         <v>8.9561838754561446E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="3">
-        <v>1.227792684649061</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" s="4">
+        <v>1.2273363178511472</v>
+      </c>
+      <c r="C9" s="4">
         <v>1.2420450482659993</v>
       </c>
-      <c r="D9" s="4">
-        <v>0.11486365922104888</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="5">
+        <v>0.11172415948983259</v>
+      </c>
+      <c r="E9" s="5">
         <v>0.10830031363337163</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
-        <v>1.2216122507945681</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="B10" s="4">
+        <v>1.2232091690544411</v>
+      </c>
+      <c r="C10" s="4">
         <v>1.2619678142187818</v>
       </c>
-      <c r="D10" s="4">
-        <v>7.0782886125654448E-2</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="5">
+        <v>6.9240536465359895E-2</v>
+      </c>
+      <c r="E10" s="5">
         <v>7.4387804582373623E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
-        <v>1.2122137404580153</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="B11" s="4">
+        <v>1.2116898849182312</v>
+      </c>
+      <c r="C11" s="4">
         <v>1.2084191260581101</v>
       </c>
-      <c r="D11" s="4">
-        <v>9.6258413426211678E-2</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="5">
+        <v>9.3780176086339109E-2</v>
+      </c>
+      <c r="E11" s="5">
         <v>9.5474203835568566E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
-        <v>1.2059145673603506</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="B12" s="4">
+        <v>1.2070460704607047</v>
+      </c>
+      <c r="C12" s="4">
         <v>1.3511652542372883</v>
       </c>
-      <c r="D12" s="4">
-        <v>9.0066094505277694E-2</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="D12" s="5">
+        <v>8.8231074554062455E-2</v>
+      </c>
+      <c r="E12" s="5">
         <v>8.5160126296797478E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
-        <v>1.2039274924471299</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B13" s="4">
+        <v>1.2031444971300225</v>
+      </c>
+      <c r="C13" s="4">
         <v>1.2147368421052631</v>
       </c>
-      <c r="D13" s="4">
-        <v>0.10165067178502879</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="D13" s="5">
+        <v>9.8726193116022376E-2</v>
+      </c>
+      <c r="E13" s="5">
         <v>0.10502111477149616</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1.1953604294478528</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1.229799723756906</v>
+      </c>
+      <c r="D14" s="5">
+        <v>8.3427968202683903E-2</v>
+      </c>
+      <c r="E14" s="5">
+        <v>8.3542478003750184E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1.1950944460107131</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1.2209902011346054</v>
+      </c>
+      <c r="D15" s="5">
+        <v>8.246727581316407E-2</v>
+      </c>
+      <c r="E15" s="5">
+        <v>8.3078043659889883E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="3">
-        <v>1.1953771289537711</v>
-      </c>
-      <c r="C14" s="3">
+      <c r="B16" s="4">
+        <v>1.194410985304746</v>
+      </c>
+      <c r="C16" s="4">
         <v>1.1943195749897833</v>
       </c>
-      <c r="D14" s="4">
-        <v>0.11808648182732366</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="D16" s="5">
+        <v>0.1153760631497026</v>
+      </c>
+      <c r="E16" s="5">
         <v>0.10163859525243504</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="3">
-        <v>1.1951975213013168</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1.229799723756906</v>
-      </c>
-      <c r="D15" s="4">
-        <v>8.5488196536767869E-2</v>
-      </c>
-      <c r="E15" s="4">
-        <v>8.3542478003750184E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="3">
-        <v>1.1949417448138677</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1.2209902011346054</v>
-      </c>
-      <c r="D16" s="4">
-        <v>8.456898416284156E-2</v>
-      </c>
-      <c r="E16" s="4">
-        <v>8.3078043659889883E-2</v>
-      </c>
-    </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="3">
-        <v>1.1933701657458562</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17" s="4">
+        <v>1.1941216678058784</v>
+      </c>
+      <c r="C17" s="4">
         <v>1.2427643236857648</v>
       </c>
-      <c r="D17" s="4">
-        <v>8.7270973963355827E-2</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="D17" s="5">
+        <v>8.543065693430657E-2</v>
+      </c>
+      <c r="E17" s="5">
         <v>8.3460685235395612E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="3">
-        <v>1.1909451511421145</v>
-      </c>
-      <c r="C18" s="3">
+      <c r="B18" s="4">
+        <v>1.1904052039571758</v>
+      </c>
+      <c r="C18" s="4">
         <v>1.201057565196491</v>
       </c>
-      <c r="D18" s="4">
-        <v>0.1286762764665505</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D18" s="5">
+        <v>0.12572411913037551</v>
+      </c>
+      <c r="E18" s="5">
         <v>0.12090083545223393</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
-        <v>1.1884270280168467</v>
-      </c>
-      <c r="C19" s="3">
+      <c r="B19" s="4">
+        <v>1.1885558583106268</v>
+      </c>
+      <c r="C19" s="4">
         <v>1.2040006350214318</v>
       </c>
-      <c r="D19" s="4">
-        <v>8.9599501222333428E-2</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="D19" s="5">
+        <v>8.7214828897338406E-2</v>
+      </c>
+      <c r="E19" s="5">
         <v>8.6923522755499125E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
-        <v>1.1674641148325358</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20" s="4">
+        <v>1.1691031212959306</v>
+      </c>
+      <c r="C20" s="4">
         <v>1.2093946410850147</v>
       </c>
-      <c r="D20" s="4">
-        <v>9.0173659799374389E-2</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="D20" s="5">
+        <v>8.8342059336823736E-2</v>
+      </c>
+      <c r="E20" s="5">
         <v>9.2698782619361569E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5">
-        <v>1.238038153420552</v>
-      </c>
-      <c r="C21" s="5">
+      <c r="B21" s="7">
+        <v>1.2381588715664438</v>
+      </c>
+      <c r="C21" s="7">
         <v>1.2531976344381792</v>
       </c>
-      <c r="D21" s="6">
-        <v>0.11011460143350159</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="D21" s="8">
+        <v>0.10773321586510184</v>
+      </c>
+      <c r="E21" s="8">
         <v>0.10435572432062265</v>
       </c>
     </row>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1B5F61-7844-4BDC-BF71-A14AB9A88F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AE15D5-5553-457D-82D3-E5AC9435B087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,6 +132,7 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -557,13 +558,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>1.412640207075065</v>
+        <v>1.4127632144391922</v>
       </c>
       <c r="C2" s="4">
         <v>1.4160828025477705</v>
       </c>
       <c r="D2" s="5">
-        <v>0.33149803360743652</v>
+        <v>0.33278512692170181</v>
       </c>
       <c r="E2" s="5">
         <v>0.13068903086175682</v>
@@ -574,13 +575,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1.3764705882352943</v>
+        <v>1.3760869565217391</v>
       </c>
       <c r="C3" s="4">
         <v>1.3706164636397193</v>
       </c>
       <c r="D3" s="5">
-        <v>0.17625374395207741</v>
+        <v>0.17663773903694033</v>
       </c>
       <c r="E3" s="5">
         <v>0.17533980582524272</v>
@@ -591,13 +592,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>1.3320288362512873</v>
+        <v>1.3316253330600534</v>
       </c>
       <c r="C4" s="4">
         <v>1.3269511305616337</v>
       </c>
       <c r="D4" s="5">
-        <v>0.2185165181384463</v>
+        <v>0.21959672337744171</v>
       </c>
       <c r="E4" s="5">
         <v>0.20836657927732816</v>
@@ -608,13 +609,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>1.2921098194410092</v>
+        <v>1.2918105574740997</v>
       </c>
       <c r="C5" s="4">
         <v>1.3297448165869219</v>
       </c>
       <c r="D5" s="5">
-        <v>8.4702086650465094E-2</v>
+        <v>8.4932540015084226E-2</v>
       </c>
       <c r="E5" s="5">
         <v>9.792093704245973E-2</v>
@@ -625,13 +626,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>1.2546975252062329</v>
+        <v>1.2549488054607509</v>
       </c>
       <c r="C6" s="4">
         <v>1.2581814618851657</v>
       </c>
       <c r="D6" s="5">
-        <v>0.14595561798692286</v>
+        <v>0.14699242462248532</v>
       </c>
       <c r="E6" s="5">
         <v>0.13729552303056392</v>
@@ -642,13 +643,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4">
-        <v>1.2306009089378891</v>
+        <v>1.2302532282408183</v>
       </c>
       <c r="C7" s="4">
         <v>1.2293759728314702</v>
       </c>
       <c r="D7" s="5">
-        <v>9.8447313039587717E-2</v>
+        <v>9.8811871344060179E-2</v>
       </c>
       <c r="E7" s="5">
         <v>0.1025868075717106</v>
@@ -659,13 +660,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>1.2297604710290377</v>
+        <v>1.2294666666666667</v>
       </c>
       <c r="C8" s="4">
         <v>1.2054814597684305</v>
       </c>
       <c r="D8" s="5">
-        <v>9.9095634647005784E-2</v>
+        <v>9.9453667851270355E-2</v>
       </c>
       <c r="E8" s="5">
         <v>8.9561838754561446E-2</v>
@@ -676,13 +677,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>1.2273363178511472</v>
+        <v>1.2276083019919206</v>
       </c>
       <c r="C9" s="4">
         <v>1.2420450482659993</v>
       </c>
       <c r="D9" s="5">
-        <v>0.11172415948983259</v>
+        <v>0.11220869347754732</v>
       </c>
       <c r="E9" s="5">
         <v>0.10830031363337163</v>
@@ -693,13 +694,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>1.2232091690544411</v>
+        <v>1.2227934875749784</v>
       </c>
       <c r="C10" s="4">
         <v>1.2619678142187818</v>
       </c>
       <c r="D10" s="5">
-        <v>6.9240536465359895E-2</v>
+        <v>6.9458773113244984E-2</v>
       </c>
       <c r="E10" s="5">
         <v>7.4387804582373623E-2</v>
@@ -710,13 +711,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>1.2116898849182312</v>
+        <v>1.2115442731943185</v>
       </c>
       <c r="C11" s="4">
         <v>1.2084191260581101</v>
       </c>
       <c r="D11" s="5">
-        <v>9.3780176086339109E-2</v>
+        <v>9.3978983243396763E-2</v>
       </c>
       <c r="E11" s="5">
         <v>9.5474203835568566E-2</v>
@@ -727,13 +728,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>1.2070460704607047</v>
+        <v>1.2070080862533692</v>
       </c>
       <c r="C12" s="4">
         <v>1.3511652542372883</v>
       </c>
       <c r="D12" s="5">
-        <v>8.8231074554062455E-2</v>
+        <v>8.8709291760317541E-2</v>
       </c>
       <c r="E12" s="5">
         <v>8.5160126296797478E-2</v>
@@ -744,13 +745,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>1.2031444971300225</v>
+        <v>1.2038786673296866</v>
       </c>
       <c r="C13" s="4">
         <v>1.2147368421052631</v>
       </c>
       <c r="D13" s="5">
-        <v>9.8726193116022376E-2</v>
+        <v>9.9095769581393059E-2</v>
       </c>
       <c r="E13" s="5">
         <v>0.10502111477149616</v>
@@ -758,53 +759,53 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
-        <v>1.1953604294478528</v>
+        <v>1.1955843532517398</v>
       </c>
       <c r="C14" s="4">
-        <v>1.229799723756906</v>
+        <v>1.1943195749897833</v>
       </c>
       <c r="D14" s="5">
-        <v>8.3427968202683903E-2</v>
+        <v>0.1158207793651676</v>
       </c>
       <c r="E14" s="5">
-        <v>8.3542478003750184E-2</v>
+        <v>0.10163859525243504</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
-        <v>1.1950944460107131</v>
+        <v>1.1953408439946533</v>
       </c>
       <c r="C15" s="4">
-        <v>1.2209902011346054</v>
+        <v>1.229799723756906</v>
       </c>
       <c r="D15" s="5">
-        <v>8.246727581316407E-2</v>
+        <v>8.3763855344604218E-2</v>
       </c>
       <c r="E15" s="5">
-        <v>8.3078043659889883E-2</v>
+        <v>8.3542478003750184E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4">
-        <v>1.194410985304746</v>
+        <v>1.1952861952861953</v>
       </c>
       <c r="C16" s="4">
-        <v>1.1943195749897833</v>
+        <v>1.2209902011346054</v>
       </c>
       <c r="D16" s="5">
-        <v>0.1153760631497026</v>
+        <v>8.2862523540489647E-2</v>
       </c>
       <c r="E16" s="5">
-        <v>0.10163859525243504</v>
+        <v>8.3078043659889883E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -812,13 +813,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="4">
-        <v>1.1941216678058784</v>
+        <v>1.1945392491467577</v>
       </c>
       <c r="C17" s="4">
         <v>1.2427643236857648</v>
       </c>
       <c r="D17" s="5">
-        <v>8.543065693430657E-2</v>
+        <v>8.5547445255474447E-2</v>
       </c>
       <c r="E17" s="5">
         <v>8.3460685235395612E-2</v>
@@ -829,13 +830,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="4">
-        <v>1.1904052039571758</v>
+        <v>1.1897622906537006</v>
       </c>
       <c r="C18" s="4">
         <v>1.201057565196491</v>
       </c>
       <c r="D18" s="5">
-        <v>0.12572411913037551</v>
+        <v>0.12615007156000818</v>
       </c>
       <c r="E18" s="5">
         <v>0.12090083545223393</v>
@@ -846,13 +847,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>1.1885558583106268</v>
+        <v>1.1885972850678734</v>
       </c>
       <c r="C19" s="4">
         <v>1.2040006350214318</v>
       </c>
       <c r="D19" s="5">
-        <v>8.7214828897338406E-2</v>
+        <v>8.7531685678073512E-2</v>
       </c>
       <c r="E19" s="5">
         <v>8.6923522755499125E-2</v>
@@ -863,13 +864,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>1.1691031212959306</v>
+        <v>1.169818754925138</v>
       </c>
       <c r="C20" s="4">
         <v>1.2093946410850147</v>
       </c>
       <c r="D20" s="5">
-        <v>8.8342059336823736E-2</v>
+        <v>8.8586387434554978E-2</v>
       </c>
       <c r="E20" s="5">
         <v>9.2698782619361569E-2</v>
@@ -880,13 +881,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2381588715664438</v>
+        <v>1.2381748686096512</v>
       </c>
       <c r="C21" s="7">
         <v>1.2531976344381792</v>
       </c>
       <c r="D21" s="8">
-        <v>0.10773321586510184</v>
+        <v>0.10816510848995081</v>
       </c>
       <c r="E21" s="8">
         <v>0.10435572432062265</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AE15D5-5553-457D-82D3-E5AC9435B087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41069B4B-90D3-4686-8F84-23BD9DBAFA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,7 +132,6 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -558,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>1.4127632144391922</v>
+        <v>1.4149049754430922</v>
       </c>
       <c r="C2" s="4">
         <v>1.4160828025477705</v>
       </c>
       <c r="D2" s="5">
-        <v>0.33278512692170181</v>
+        <v>0.33485877726135144</v>
       </c>
       <c r="E2" s="5">
         <v>0.13068903086175682</v>
@@ -575,13 +574,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1.3760869565217391</v>
+        <v>1.3751617076326001</v>
       </c>
       <c r="C3" s="4">
         <v>1.3706164636397193</v>
       </c>
       <c r="D3" s="5">
-        <v>0.17663773903694033</v>
+        <v>0.1780969203594194</v>
       </c>
       <c r="E3" s="5">
         <v>0.17533980582524272</v>
@@ -592,13 +591,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>1.3316253330600534</v>
+        <v>1.3323164531218223</v>
       </c>
       <c r="C4" s="4">
         <v>1.3269511305616337</v>
       </c>
       <c r="D4" s="5">
-        <v>0.21959672337744171</v>
+        <v>0.22130704833918444</v>
       </c>
       <c r="E4" s="5">
         <v>0.20836657927732816</v>
@@ -609,13 +608,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>1.2918105574740997</v>
+        <v>1.2914831130690163</v>
       </c>
       <c r="C5" s="4">
         <v>1.3297448165869219</v>
       </c>
       <c r="D5" s="5">
-        <v>8.4932540015084226E-2</v>
+        <v>8.5602949803067124E-2</v>
       </c>
       <c r="E5" s="5">
         <v>9.792093704245973E-2</v>
@@ -626,13 +625,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>1.2549488054607509</v>
+        <v>1.2546562817473754</v>
       </c>
       <c r="C6" s="4">
         <v>1.2581814618851657</v>
       </c>
       <c r="D6" s="5">
-        <v>0.14699242462248532</v>
+        <v>0.14814629007174032</v>
       </c>
       <c r="E6" s="5">
         <v>0.13729552303056392</v>
@@ -643,13 +642,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4">
-        <v>1.2302532282408183</v>
+        <v>1.2306285334220155</v>
       </c>
       <c r="C7" s="4">
         <v>1.2293759728314702</v>
       </c>
       <c r="D7" s="5">
-        <v>9.8811871344060179E-2</v>
+        <v>9.9656983777155456E-2</v>
       </c>
       <c r="E7" s="5">
         <v>0.1025868075717106</v>
@@ -660,13 +659,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>1.2294666666666667</v>
+        <v>1.2292631300436565</v>
       </c>
       <c r="C8" s="4">
         <v>1.2054814597684305</v>
       </c>
       <c r="D8" s="5">
-        <v>9.9453667851270355E-2</v>
+        <v>0.10023603670503368</v>
       </c>
       <c r="E8" s="5">
         <v>8.9561838754561446E-2</v>
@@ -677,13 +676,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>1.2276083019919206</v>
+        <v>1.2272539003175482</v>
       </c>
       <c r="C9" s="4">
         <v>1.2420450482659993</v>
       </c>
       <c r="D9" s="5">
-        <v>0.11220869347754732</v>
+        <v>0.11320902171024867</v>
       </c>
       <c r="E9" s="5">
         <v>0.10830031363337163</v>
@@ -694,13 +693,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>1.2227934875749784</v>
+        <v>1.224858757062147</v>
       </c>
       <c r="C10" s="4">
         <v>1.2619678142187818</v>
       </c>
       <c r="D10" s="5">
-        <v>6.9458773113244984E-2</v>
+        <v>7.0232521228473926E-2</v>
       </c>
       <c r="E10" s="5">
         <v>7.4387804582373623E-2</v>
@@ -711,13 +710,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>1.2115442731943185</v>
+        <v>1.2111577684463108</v>
       </c>
       <c r="C11" s="4">
         <v>1.2084191260581101</v>
       </c>
       <c r="D11" s="5">
-        <v>9.3978983243396763E-2</v>
+        <v>9.4689008804316951E-2</v>
       </c>
       <c r="E11" s="5">
         <v>9.5474203835568566E-2</v>
@@ -728,13 +727,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>1.2070080862533692</v>
+        <v>1.2064343163538873</v>
       </c>
       <c r="C12" s="4">
         <v>1.3511652542372883</v>
       </c>
       <c r="D12" s="5">
-        <v>8.8709291760317541E-2</v>
+        <v>8.9187508966572612E-2</v>
       </c>
       <c r="E12" s="5">
         <v>8.5160126296797478E-2</v>
@@ -745,13 +744,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>1.2038786673296866</v>
+        <v>1.2040463853935357</v>
       </c>
       <c r="C13" s="4">
         <v>1.2147368421052631</v>
       </c>
       <c r="D13" s="5">
-        <v>9.9095769581393059E-2</v>
+        <v>9.9859560943159134E-2</v>
       </c>
       <c r="E13" s="5">
         <v>0.10502111477149616</v>
@@ -762,13 +761,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="4">
-        <v>1.1955843532517398</v>
+        <v>1.1955120553831464</v>
       </c>
       <c r="C14" s="4">
         <v>1.1943195749897833</v>
       </c>
       <c r="D14" s="5">
-        <v>0.1158207793651676</v>
+        <v>0.11643226416143199</v>
       </c>
       <c r="E14" s="5">
         <v>0.10163859525243504</v>
@@ -776,19 +775,19 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4">
-        <v>1.1953408439946533</v>
+        <v>1.1948579161028416</v>
       </c>
       <c r="C15" s="4">
-        <v>1.229799723756906</v>
+        <v>1.2427643236857648</v>
       </c>
       <c r="D15" s="5">
-        <v>8.3763855344604218E-2</v>
+        <v>8.6306569343065687E-2</v>
       </c>
       <c r="E15" s="5">
-        <v>8.3542478003750184E-2</v>
+        <v>8.3460685235395612E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -796,13 +795,13 @@
         <v>17</v>
       </c>
       <c r="B16" s="4">
-        <v>1.1952861952861953</v>
+        <v>1.1948232674645143</v>
       </c>
       <c r="C16" s="4">
         <v>1.2209902011346054</v>
       </c>
       <c r="D16" s="5">
-        <v>8.2862523540489647E-2</v>
+        <v>8.3536769663574428E-2</v>
       </c>
       <c r="E16" s="5">
         <v>8.3078043659889883E-2</v>
@@ -810,19 +809,19 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="4">
-        <v>1.1945392491467577</v>
+        <v>1.1945966370678254</v>
       </c>
       <c r="C17" s="4">
-        <v>1.2427643236857648</v>
+        <v>1.229799723756906</v>
       </c>
       <c r="D17" s="5">
-        <v>8.5547445255474447E-2</v>
+        <v>8.4659554389725056E-2</v>
       </c>
       <c r="E17" s="5">
-        <v>8.3460685235395612E-2</v>
+        <v>8.3542478003750184E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -830,13 +829,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="4">
-        <v>1.1897622906537006</v>
+        <v>1.1906677393403058</v>
       </c>
       <c r="C18" s="4">
         <v>1.201057565196491</v>
       </c>
       <c r="D18" s="5">
-        <v>0.12615007156000818</v>
+        <v>0.12707012880801472</v>
       </c>
       <c r="E18" s="5">
         <v>0.12090083545223393</v>
@@ -847,13 +846,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>1.1885972850678734</v>
+        <v>1.1881401617250673</v>
       </c>
       <c r="C19" s="4">
         <v>1.2040006350214318</v>
       </c>
       <c r="D19" s="5">
-        <v>8.7531685678073512E-2</v>
+        <v>8.8165399239543724E-2</v>
       </c>
       <c r="E19" s="5">
         <v>8.6923522755499125E-2</v>
@@ -864,13 +863,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>1.169818754925138</v>
+        <v>1.1715628672150411</v>
       </c>
       <c r="C20" s="4">
         <v>1.2093946410850147</v>
       </c>
       <c r="D20" s="5">
-        <v>8.8586387434554978E-2</v>
+        <v>8.9109947643979059E-2</v>
       </c>
       <c r="E20" s="5">
         <v>9.2698782619361569E-2</v>
@@ -881,13 +880,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2381748686096512</v>
+        <v>1.2383268811864425</v>
       </c>
       <c r="C21" s="7">
         <v>1.2531976344381792</v>
       </c>
       <c r="D21" s="8">
-        <v>0.10816510848995081</v>
+        <v>0.10902028049641813</v>
       </c>
       <c r="E21" s="8">
         <v>0.10435572432062265</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41069B4B-90D3-4686-8F84-23BD9DBAFA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88CCB3D-1F4A-4867-8418-55AED6B97DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,9 +129,9 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -177,18 +177,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -557,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>1.4149049754430922</v>
+        <v>1.4149819110449033</v>
       </c>
       <c r="C2" s="4">
         <v>1.4160828025477705</v>
       </c>
       <c r="D2" s="5">
-        <v>0.33485877726135144</v>
+        <v>0.33600286020736503</v>
       </c>
       <c r="E2" s="5">
         <v>0.13068903086175682</v>
@@ -574,13 +574,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1.3751617076326001</v>
+        <v>1.3740883740883743</v>
       </c>
       <c r="C3" s="4">
         <v>1.3706164636397193</v>
       </c>
       <c r="D3" s="5">
-        <v>0.1780969203594194</v>
+        <v>0.1790185085630904</v>
       </c>
       <c r="E3" s="5">
         <v>0.17533980582524272</v>
@@ -591,13 +591,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>1.3323164531218223</v>
+        <v>1.3336035670855291</v>
       </c>
       <c r="C4" s="4">
         <v>1.3269511305616337</v>
       </c>
       <c r="D4" s="5">
-        <v>0.22130704833918444</v>
+        <v>0.2220721937168062</v>
       </c>
       <c r="E4" s="5">
         <v>0.20836657927732816</v>
@@ -608,13 +608,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>1.2914831130690163</v>
+        <v>1.2918695228821813</v>
       </c>
       <c r="C5" s="4">
         <v>1.3297448165869219</v>
       </c>
       <c r="D5" s="5">
-        <v>8.5602949803067124E-2</v>
+        <v>8.6063856532305374E-2</v>
       </c>
       <c r="E5" s="5">
         <v>9.792093704245973E-2</v>
@@ -625,13 +625,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>1.2546562817473754</v>
+        <v>1.2547785023611424</v>
       </c>
       <c r="C6" s="4">
         <v>1.2581814618851657</v>
       </c>
       <c r="D6" s="5">
-        <v>0.14814629007174032</v>
+        <v>0.14873158414020302</v>
       </c>
       <c r="E6" s="5">
         <v>0.13729552303056392</v>
@@ -642,13 +642,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4">
-        <v>1.2306285334220155</v>
+        <v>1.2305017386984598</v>
       </c>
       <c r="C7" s="4">
         <v>1.2293759728314702</v>
       </c>
       <c r="D7" s="5">
-        <v>9.9656983777155456E-2</v>
+        <v>0.10007125457769235</v>
       </c>
       <c r="E7" s="5">
         <v>0.1025868075717106</v>
@@ -659,13 +659,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>1.2292631300436565</v>
+        <v>1.2295319709953856</v>
       </c>
       <c r="C8" s="4">
         <v>1.2054814597684305</v>
       </c>
       <c r="D8" s="5">
-        <v>0.10023603670503368</v>
+        <v>0.10058080942025142</v>
       </c>
       <c r="E8" s="5">
         <v>8.9561838754561446E-2</v>
@@ -676,13 +676,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>1.2272539003175482</v>
+        <v>1.2281353135313531</v>
       </c>
       <c r="C9" s="4">
         <v>1.2420450482659993</v>
       </c>
       <c r="D9" s="5">
-        <v>0.11320902171024867</v>
+        <v>0.11366229544069148</v>
       </c>
       <c r="E9" s="5">
         <v>0.10830031363337163</v>
@@ -693,13 +693,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>1.224858757062147</v>
+        <v>1.2257882882882882</v>
       </c>
       <c r="C10" s="4">
         <v>1.2619678142187818</v>
       </c>
       <c r="D10" s="5">
-        <v>7.0232521228473926E-2</v>
+        <v>7.0470597571621302E-2</v>
       </c>
       <c r="E10" s="5">
         <v>7.4387804582373623E-2</v>
@@ -710,13 +710,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>1.2111577684463108</v>
+        <v>1.2108091967751569</v>
       </c>
       <c r="C11" s="4">
         <v>1.2084191260581101</v>
       </c>
       <c r="D11" s="5">
-        <v>9.4689008804316951E-2</v>
+        <v>9.5115024140869073E-2</v>
       </c>
       <c r="E11" s="5">
         <v>9.5474203835568566E-2</v>
@@ -727,13 +727,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>1.2064343163538873</v>
+        <v>1.2065101387406616</v>
       </c>
       <c r="C12" s="4">
         <v>1.3511652542372883</v>
       </c>
       <c r="D12" s="5">
-        <v>8.9187508966572612E-2</v>
+        <v>8.9617904452202191E-2</v>
       </c>
       <c r="E12" s="5">
         <v>8.5160126296797478E-2</v>
@@ -744,13 +744,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>1.2040463853935357</v>
+        <v>1.2038310412573674</v>
       </c>
       <c r="C13" s="4">
         <v>1.2147368421052631</v>
       </c>
       <c r="D13" s="5">
-        <v>9.9859560943159134E-2</v>
+        <v>0.10032769113262867</v>
       </c>
       <c r="E13" s="5">
         <v>0.10502111477149616</v>
@@ -758,36 +758,36 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>1.1955120553831464</v>
+        <v>1.1952861952861953</v>
       </c>
       <c r="C14" s="4">
-        <v>1.1943195749897833</v>
+        <v>1.2427643236857648</v>
       </c>
       <c r="D14" s="5">
-        <v>0.11643226416143199</v>
+        <v>8.6715328467153283E-2</v>
       </c>
       <c r="E14" s="5">
-        <v>0.10163859525243504</v>
+        <v>8.3460685235395612E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>1.1948579161028416</v>
+        <v>1.1949595815501663</v>
       </c>
       <c r="C15" s="4">
-        <v>1.2427643236857648</v>
+        <v>1.1943195749897833</v>
       </c>
       <c r="D15" s="5">
-        <v>8.6306569343065687E-2</v>
+        <v>0.11690477514036356</v>
       </c>
       <c r="E15" s="5">
-        <v>8.3460685235395612E-2</v>
+        <v>0.10163859525243504</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -795,13 +795,13 @@
         <v>17</v>
       </c>
       <c r="B16" s="4">
-        <v>1.1948232674645143</v>
+        <v>1.1945676274944568</v>
       </c>
       <c r="C16" s="4">
         <v>1.2209902011346054</v>
       </c>
       <c r="D16" s="5">
-        <v>8.3536769663574428E-2</v>
+        <v>8.388551765827347E-2</v>
       </c>
       <c r="E16" s="5">
         <v>8.3078043659889883E-2</v>
@@ -812,13 +812,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="4">
-        <v>1.1945966370678254</v>
+        <v>1.1943502824858756</v>
       </c>
       <c r="C17" s="4">
         <v>1.229799723756906</v>
       </c>
       <c r="D17" s="5">
-        <v>8.4659554389725056E-2</v>
+        <v>8.4931463028422444E-2</v>
       </c>
       <c r="E17" s="5">
         <v>8.3542478003750184E-2</v>
@@ -829,13 +829,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="4">
-        <v>1.1906677393403058</v>
+        <v>1.1902980088199919</v>
       </c>
       <c r="C18" s="4">
         <v>1.201057565196491</v>
       </c>
       <c r="D18" s="5">
-        <v>0.12707012880801472</v>
+        <v>0.12749608123764739</v>
       </c>
       <c r="E18" s="5">
         <v>0.12090083545223393</v>
@@ -846,13 +846,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>1.1881401617250673</v>
+        <v>1.1877572937175587</v>
       </c>
       <c r="C19" s="4">
         <v>1.2040006350214318</v>
       </c>
       <c r="D19" s="5">
-        <v>8.8165399239543724E-2</v>
+        <v>8.8513941698352347E-2</v>
       </c>
       <c r="E19" s="5">
         <v>8.6923522755499125E-2</v>
@@ -863,13 +863,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>1.1715628672150411</v>
+        <v>1.1712168486739469</v>
       </c>
       <c r="C20" s="4">
         <v>1.2093946410850147</v>
       </c>
       <c r="D20" s="5">
-        <v>8.9109947643979059E-2</v>
+        <v>8.9493891797556721E-2</v>
       </c>
       <c r="E20" s="5">
         <v>9.2698782619361569E-2</v>
@@ -880,13 +880,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2383268811864425</v>
+        <v>1.2383982372515514</v>
       </c>
       <c r="C21" s="7">
         <v>1.2531976344381792</v>
       </c>
       <c r="D21" s="8">
-        <v>0.10902028049641813</v>
+        <v>0.10945217312126708</v>
       </c>
       <c r="E21" s="8">
         <v>0.10435572432062265</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88CCB3D-1F4A-4867-8418-55AED6B97DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AF681B-5696-458B-81A4-25B7D51DAAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,8 +129,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -177,18 +178,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -557,13 +558,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>1.4149819110449033</v>
+        <v>1.4158291457286432</v>
       </c>
       <c r="C2" s="4">
         <v>1.4160828025477705</v>
       </c>
       <c r="D2" s="5">
-        <v>0.33600286020736503</v>
+        <v>0.32694414019715223</v>
       </c>
       <c r="E2" s="5">
         <v>0.13068903086175682</v>
@@ -574,13 +575,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1.3740883740883743</v>
+        <v>1.3718166383701189</v>
       </c>
       <c r="C3" s="4">
         <v>1.3706164636397193</v>
       </c>
       <c r="D3" s="5">
-        <v>0.1790185085630904</v>
+        <v>0.17486825502857567</v>
       </c>
       <c r="E3" s="5">
         <v>0.17533980582524272</v>
@@ -591,13 +592,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>1.3336035670855291</v>
+        <v>1.3347398030942335</v>
       </c>
       <c r="C4" s="4">
         <v>1.3269511305616337</v>
       </c>
       <c r="D4" s="5">
-        <v>0.2220721937168062</v>
+        <v>0.21728880157170924</v>
       </c>
       <c r="E4" s="5">
         <v>0.20836657927732816</v>
@@ -608,13 +609,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>1.2918695228821813</v>
+        <v>1.2934390771449171</v>
       </c>
       <c r="C5" s="4">
         <v>1.3297448165869219</v>
       </c>
       <c r="D5" s="5">
-        <v>8.6063856532305374E-2</v>
+        <v>8.4418746195982955E-2</v>
       </c>
       <c r="E5" s="5">
         <v>9.792093704245973E-2</v>
@@ -625,13 +626,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>1.2547785023611424</v>
+        <v>1.2551247771836007</v>
       </c>
       <c r="C6" s="4">
         <v>1.2581814618851657</v>
       </c>
       <c r="D6" s="5">
-        <v>0.14873158414020302</v>
+        <v>0.15010284452917272</v>
       </c>
       <c r="E6" s="5">
         <v>0.13729552303056392</v>
@@ -642,13 +643,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4">
-        <v>1.2305017386984598</v>
+        <v>1.2332461588754495</v>
       </c>
       <c r="C7" s="4">
         <v>1.2293759728314702</v>
       </c>
       <c r="D7" s="5">
-        <v>0.10007125457769235</v>
+        <v>9.7372316213334184E-2</v>
       </c>
       <c r="E7" s="5">
         <v>0.1025868075717106</v>
@@ -659,13 +660,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>1.2295319709953856</v>
+        <v>1.2288764483791172</v>
       </c>
       <c r="C8" s="4">
         <v>1.2054814597684305</v>
       </c>
       <c r="D8" s="5">
-        <v>0.10058080942025142</v>
+        <v>9.8447853782955869E-2</v>
       </c>
       <c r="E8" s="5">
         <v>8.9561838754561446E-2</v>
@@ -676,13 +677,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>1.2281353135313531</v>
+        <v>1.2282416836388321</v>
       </c>
       <c r="C9" s="4">
         <v>1.2420450482659993</v>
       </c>
       <c r="D9" s="5">
-        <v>0.11366229544069148</v>
+        <v>0.11067864871363309</v>
       </c>
       <c r="E9" s="5">
         <v>0.10830031363337163</v>
@@ -693,13 +694,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>1.2257882882882882</v>
+        <v>1.225125069483046</v>
       </c>
       <c r="C10" s="4">
         <v>1.2619678142187818</v>
       </c>
       <c r="D10" s="5">
-        <v>7.0470597571621302E-2</v>
+        <v>6.864971093854344E-2</v>
       </c>
       <c r="E10" s="5">
         <v>7.4387804582373623E-2</v>
@@ -710,13 +711,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>1.2108091967751569</v>
+        <v>1.210495283018868</v>
       </c>
       <c r="C11" s="4">
         <v>1.2084191260581101</v>
       </c>
       <c r="D11" s="5">
-        <v>9.5115024140869073E-2</v>
+        <v>9.2728266812465834E-2</v>
       </c>
       <c r="E11" s="5">
         <v>9.5474203835568566E-2</v>
@@ -727,13 +728,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>1.2065101387406616</v>
+        <v>1.2071503680336488</v>
       </c>
       <c r="C12" s="4">
         <v>1.3511652542372883</v>
       </c>
       <c r="D12" s="5">
-        <v>8.9617904452202191E-2</v>
+        <v>8.7645730611492556E-2</v>
       </c>
       <c r="E12" s="5">
         <v>8.5160126296797478E-2</v>
@@ -744,13 +745,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>1.2038310412573674</v>
+        <v>1.2030642023346303</v>
       </c>
       <c r="C13" s="4">
         <v>1.2147368421052631</v>
       </c>
       <c r="D13" s="5">
-        <v>0.10032769113262867</v>
+        <v>9.8122032118739114E-2</v>
       </c>
       <c r="E13" s="5">
         <v>0.10502111477149616</v>
@@ -761,13 +762,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>1.1952861952861953</v>
+        <v>1.1981382978723405</v>
       </c>
       <c r="C14" s="4">
         <v>1.2427643236857648</v>
       </c>
       <c r="D14" s="5">
-        <v>8.6715328467153283E-2</v>
+        <v>8.4508625049165592E-2</v>
       </c>
       <c r="E14" s="5">
         <v>8.3460685235395612E-2</v>
@@ -778,13 +779,13 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>1.1949595815501663</v>
+        <v>1.1955399061032863</v>
       </c>
       <c r="C15" s="4">
         <v>1.1943195749897833</v>
       </c>
       <c r="D15" s="5">
-        <v>0.11690477514036356</v>
+        <v>0.11465482438433588</v>
       </c>
       <c r="E15" s="5">
         <v>0.10163859525243504</v>
@@ -792,36 +793,36 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4">
-        <v>1.1945676274944568</v>
+        <v>1.1951174058889302</v>
       </c>
       <c r="C16" s="4">
-        <v>1.2209902011346054</v>
+        <v>1.229799723756906</v>
       </c>
       <c r="D16" s="5">
-        <v>8.388551765827347E-2</v>
+        <v>8.2816310152174583E-2</v>
       </c>
       <c r="E16" s="5">
-        <v>8.3078043659889883E-2</v>
+        <v>8.3542478003750184E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>1.1943502824858756</v>
+        <v>1.1941482089144106</v>
       </c>
       <c r="C17" s="4">
-        <v>1.229799723756906</v>
+        <v>1.2209902011346054</v>
       </c>
       <c r="D17" s="5">
-        <v>8.4931463028422444E-2</v>
+        <v>8.2161312064704561E-2</v>
       </c>
       <c r="E17" s="5">
-        <v>8.3542478003750184E-2</v>
+        <v>8.3078043659889883E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -829,13 +830,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="4">
-        <v>1.1902980088199919</v>
+        <v>1.1900303310035605</v>
       </c>
       <c r="C18" s="4">
         <v>1.201057565196491</v>
       </c>
       <c r="D18" s="5">
-        <v>0.12749608123764739</v>
+        <v>0.12486415280750865</v>
       </c>
       <c r="E18" s="5">
         <v>0.12090083545223393</v>
@@ -846,13 +847,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>1.1877572937175587</v>
+        <v>1.1883852691218131</v>
       </c>
       <c r="C19" s="4">
         <v>1.2040006350214318</v>
       </c>
       <c r="D19" s="5">
-        <v>8.8513941698352347E-2</v>
+        <v>8.6702895213533512E-2</v>
       </c>
       <c r="E19" s="5">
         <v>8.6923522755499125E-2</v>
@@ -863,13 +864,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>1.1712168486739469</v>
+        <v>1.1733282090699462</v>
       </c>
       <c r="C20" s="4">
         <v>1.2093946410850147</v>
       </c>
       <c r="D20" s="5">
-        <v>8.9493891797556721E-2</v>
+        <v>8.7368208985293128E-2</v>
       </c>
       <c r="E20" s="5">
         <v>9.2698782619361569E-2</v>
@@ -880,13 +881,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2383982372515514</v>
+        <v>1.2388208898860429</v>
       </c>
       <c r="C21" s="7">
         <v>1.2531976344381792</v>
       </c>
       <c r="D21" s="8">
-        <v>0.10945217312126708</v>
+        <v>0.10718588537822329</v>
       </c>
       <c r="E21" s="8">
         <v>0.10435572432062265</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AF681B-5696-458B-81A4-25B7D51DAAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323A1138-20BA-4830-8DD5-89773DFB94C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,7 +132,6 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -558,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>1.4158291457286432</v>
+        <v>1.415484140233723</v>
       </c>
       <c r="C2" s="4">
         <v>1.4160828025477705</v>
       </c>
       <c r="D2" s="5">
-        <v>0.32694414019715223</v>
+        <v>0.32803943044906902</v>
       </c>
       <c r="E2" s="5">
         <v>0.13068903086175682</v>
@@ -575,13 +574,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1.3718166383701189</v>
+        <v>1.3718763235916984</v>
       </c>
       <c r="C3" s="4">
         <v>1.3706164636397193</v>
       </c>
       <c r="D3" s="5">
-        <v>0.17486825502857567</v>
+        <v>0.17523936762413717</v>
       </c>
       <c r="E3" s="5">
         <v>0.17533980582524272</v>
@@ -592,13 +591,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>1.3347398030942335</v>
+        <v>1.3339346562437364</v>
       </c>
       <c r="C4" s="4">
         <v>1.3269511305616337</v>
       </c>
       <c r="D4" s="5">
-        <v>0.21728880157170924</v>
+        <v>0.21781270464963981</v>
       </c>
       <c r="E4" s="5">
         <v>0.20836657927732816</v>
@@ -609,13 +608,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>1.2934390771449171</v>
+        <v>1.2935120900167585</v>
       </c>
       <c r="C5" s="4">
         <v>1.3297448165869219</v>
       </c>
       <c r="D5" s="5">
-        <v>8.4418746195982955E-2</v>
+        <v>8.4743355650233318E-2</v>
       </c>
       <c r="E5" s="5">
         <v>9.792093704245973E-2</v>
@@ -626,13 +625,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>1.2551247771836007</v>
+        <v>1.2551655187736059</v>
       </c>
       <c r="C6" s="4">
         <v>1.2581814618851657</v>
       </c>
       <c r="D6" s="5">
-        <v>0.15010284452917272</v>
+        <v>0.15053763440860216</v>
       </c>
       <c r="E6" s="5">
         <v>0.13729552303056392</v>
@@ -643,13 +642,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4">
-        <v>1.2332461588754495</v>
+        <v>1.2337408312958436</v>
       </c>
       <c r="C7" s="4">
         <v>1.2293759728314702</v>
       </c>
       <c r="D7" s="5">
-        <v>9.7372316213334184E-2</v>
+        <v>9.7642883290095656E-2</v>
       </c>
       <c r="E7" s="5">
         <v>0.1025868075717106</v>
@@ -657,36 +656,36 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>1.2288764483791172</v>
+        <v>1.2287068381855113</v>
       </c>
       <c r="C8" s="4">
-        <v>1.2054814597684305</v>
+        <v>1.2420450482659993</v>
       </c>
       <c r="D8" s="5">
-        <v>9.8447853782955869E-2</v>
+        <v>0.11097920173118538</v>
       </c>
       <c r="E8" s="5">
-        <v>8.9561838754561446E-2</v>
+        <v>0.10830031363337163</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>1.2282416836388321</v>
+        <v>1.2284527518172377</v>
       </c>
       <c r="C9" s="4">
-        <v>1.2420450482659993</v>
+        <v>1.2054814597684305</v>
       </c>
       <c r="D9" s="5">
-        <v>0.11067864871363309</v>
+        <v>9.8742646210635596E-2</v>
       </c>
       <c r="E9" s="5">
-        <v>0.10830031363337163</v>
+        <v>8.9561838754561446E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -694,13 +693,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>1.225125069483046</v>
+        <v>1.2250830564784052</v>
       </c>
       <c r="C10" s="4">
         <v>1.2619678142187818</v>
       </c>
       <c r="D10" s="5">
-        <v>6.864971093854344E-2</v>
+        <v>6.8916830436358781E-2</v>
       </c>
       <c r="E10" s="5">
         <v>7.4387804582373623E-2</v>
@@ -711,13 +710,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>1.210495283018868</v>
+        <v>1.21023228462217</v>
       </c>
       <c r="C11" s="4">
         <v>1.2084191260581101</v>
       </c>
       <c r="D11" s="5">
-        <v>9.2728266812465834E-2</v>
+        <v>9.2974302897758335E-2</v>
       </c>
       <c r="E11" s="5">
         <v>9.5474203835568566E-2</v>
@@ -728,13 +727,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>1.2071503680336488</v>
+        <v>1.2078534031413612</v>
       </c>
       <c r="C12" s="4">
         <v>1.3511652542372883</v>
       </c>
       <c r="D12" s="5">
-        <v>8.7645730611492556E-2</v>
+        <v>8.8014377217639744E-2</v>
       </c>
       <c r="E12" s="5">
         <v>8.5160126296797478E-2</v>
@@ -745,13 +744,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>1.2030642023346303</v>
+        <v>1.2029547105836764</v>
       </c>
       <c r="C13" s="4">
         <v>1.2147368421052631</v>
       </c>
       <c r="D13" s="5">
-        <v>9.8122032118739114E-2</v>
+        <v>9.8527692270980988E-2</v>
       </c>
       <c r="E13" s="5">
         <v>0.10502111477149616</v>
@@ -762,13 +761,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>1.1981382978723405</v>
+        <v>1.1980066445182724</v>
       </c>
       <c r="C14" s="4">
         <v>1.2427643236857648</v>
       </c>
       <c r="D14" s="5">
-        <v>8.4508625049165592E-2</v>
+        <v>8.456481429454403E-2</v>
       </c>
       <c r="E14" s="5">
         <v>8.3460685235395612E-2</v>
@@ -779,13 +778,13 @@
         <v>16</v>
       </c>
       <c r="B15" s="4">
-        <v>1.1955399061032863</v>
+        <v>1.1953216374269005</v>
       </c>
       <c r="C15" s="4">
         <v>1.1943195749897833</v>
       </c>
       <c r="D15" s="5">
-        <v>0.11465482438433588</v>
+        <v>0.11505853855470327</v>
       </c>
       <c r="E15" s="5">
         <v>0.10163859525243504</v>
@@ -796,13 +795,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="4">
-        <v>1.1951174058889302</v>
+        <v>1.1947955390334573</v>
       </c>
       <c r="C16" s="4">
         <v>1.229799723756906</v>
       </c>
       <c r="D16" s="5">
-        <v>8.2816310152174583E-2</v>
+        <v>8.3032379541315551E-2</v>
       </c>
       <c r="E16" s="5">
         <v>8.3542478003750184E-2</v>
@@ -813,13 +812,13 @@
         <v>17</v>
       </c>
       <c r="B17" s="4">
-        <v>1.1941482089144106</v>
+        <v>1.1943385955362003</v>
       </c>
       <c r="C17" s="4">
         <v>1.2209902011346054</v>
       </c>
       <c r="D17" s="5">
-        <v>8.2161312064704561E-2</v>
+        <v>8.2543248708155464E-2</v>
       </c>
       <c r="E17" s="5">
         <v>8.3078043659889883E-2</v>
@@ -830,13 +829,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="4">
-        <v>1.1900303310035605</v>
+        <v>1.190376018932422</v>
       </c>
       <c r="C18" s="4">
         <v>1.201057565196491</v>
       </c>
       <c r="D18" s="5">
-        <v>0.12486415280750865</v>
+        <v>0.12524287831384817</v>
       </c>
       <c r="E18" s="5">
         <v>0.12090083545223393</v>
@@ -847,13 +846,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>1.1883852691218131</v>
+        <v>1.1882166166872465</v>
       </c>
       <c r="C19" s="4">
         <v>1.2040006350214318</v>
       </c>
       <c r="D19" s="5">
-        <v>8.6702895213533512E-2</v>
+        <v>8.7025267876331705E-2</v>
       </c>
       <c r="E19" s="5">
         <v>8.6923522755499125E-2</v>
@@ -864,13 +863,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>1.1733282090699462</v>
+        <v>1.1733793632527809</v>
       </c>
       <c r="C20" s="4">
         <v>1.2093946410850147</v>
       </c>
       <c r="D20" s="5">
-        <v>8.7368208985293128E-2</v>
+        <v>8.7536095628231822E-2</v>
       </c>
       <c r="E20" s="5">
         <v>9.2698782619361569E-2</v>
@@ -881,13 +880,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2388208898860429</v>
+        <v>1.2387917575542835</v>
       </c>
       <c r="C21" s="7">
         <v>1.2531976344381792</v>
       </c>
       <c r="D21" s="8">
-        <v>0.10718588537822329</v>
+        <v>0.1075180361437177</v>
       </c>
       <c r="E21" s="8">
         <v>0.10435572432062265</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323A1138-20BA-4830-8DD5-89773DFB94C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFC53E0-F766-4291-A82D-73E0F3029924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,6 +132,7 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -177,19 +178,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -553,342 +558,342 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>1.415484140233723</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2" s="3">
+        <v>1.4166493668258251</v>
+      </c>
+      <c r="C2" s="3">
         <v>1.4160828025477705</v>
       </c>
-      <c r="D2" s="5">
-        <v>0.32803943044906902</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="4">
+        <v>0.32975082146768891</v>
+      </c>
+      <c r="E2" s="4">
         <v>0.13068903086175682</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
-        <v>1.3718763235916984</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="3">
+        <v>1.3720637583892616</v>
+      </c>
+      <c r="C3" s="3">
         <v>1.3706164636397193</v>
       </c>
-      <c r="D3" s="5">
-        <v>0.17523936762413717</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3" s="4">
+        <v>0.17694648556372003</v>
+      </c>
+      <c r="E3" s="4">
         <v>0.17533980582524272</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
-        <v>1.3339346562437364</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="3">
+        <v>1.3345977240966262</v>
+      </c>
+      <c r="C4" s="3">
         <v>1.3269511305616337</v>
       </c>
-      <c r="D4" s="5">
-        <v>0.21781270464963981</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="4">
+        <v>0.21868587644619078</v>
+      </c>
+      <c r="E4" s="4">
         <v>0.20836657927732816</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>1.2935120900167585</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="B5" s="3">
+        <v>1.2933206560494415</v>
+      </c>
+      <c r="C5" s="3">
         <v>1.3297448165869219</v>
       </c>
-      <c r="D5" s="5">
-        <v>8.4743355650233318E-2</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="4">
+        <v>8.5351998376952731E-2</v>
+      </c>
+      <c r="E5" s="4">
         <v>9.792093704245973E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>1.2551655187736059</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="B6" s="3">
+        <v>1.2547658402203856</v>
+      </c>
+      <c r="C6" s="3">
         <v>1.2581814618851657</v>
       </c>
-      <c r="D6" s="5">
-        <v>0.15053763440860216</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6" s="4">
+        <v>0.1517583906085386</v>
+      </c>
+      <c r="E6" s="4">
         <v>0.13729552303056392</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4">
-        <v>1.2337408312958436</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="3">
+        <v>1.2343800582712852</v>
+      </c>
+      <c r="C7" s="3">
         <v>1.2293759728314702</v>
       </c>
-      <c r="D7" s="5">
-        <v>9.7642883290095656E-2</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" s="4">
+        <v>9.83272588371982E-2</v>
+      </c>
+      <c r="E7" s="4">
         <v>0.1025868075717106</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
-        <v>1.2287068381855113</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="B8" s="3">
+        <v>1.2304382898628663</v>
+      </c>
+      <c r="C8" s="3">
         <v>1.2420450482659993</v>
       </c>
-      <c r="D8" s="5">
-        <v>0.11097920173118538</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="4">
+        <v>0.11177566722769897</v>
+      </c>
+      <c r="E8" s="4">
         <v>0.10830031363337163</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
-        <v>1.2284527518172377</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="B9" s="3">
+        <v>1.229112944816916</v>
+      </c>
+      <c r="C9" s="3">
         <v>1.2054814597684305</v>
       </c>
-      <c r="D9" s="5">
-        <v>9.8742646210635596E-2</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" s="4">
+        <v>9.9409133438433245E-2</v>
+      </c>
+      <c r="E9" s="4">
         <v>8.9561838754561446E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
-        <v>1.2250830564784052</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="B10" s="3">
+        <v>1.2260726072607262</v>
+      </c>
+      <c r="C10" s="3">
         <v>1.2619678142187818</v>
       </c>
-      <c r="D10" s="5">
-        <v>6.8916830436358781E-2</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="4">
+        <v>6.9374749575470795E-2</v>
+      </c>
+      <c r="E10" s="4">
         <v>7.4387804582373623E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
-        <v>1.21023228462217</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="B11" s="3">
+        <v>1.2117578239251243</v>
+      </c>
+      <c r="C11" s="3">
         <v>1.2084191260581101</v>
       </c>
-      <c r="D11" s="5">
-        <v>9.2974302897758335E-2</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="4">
+        <v>9.3466375068343363E-2</v>
+      </c>
+      <c r="E11" s="4">
         <v>9.5474203835568566E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
-        <v>1.2078534031413612</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="B12" s="3">
+        <v>1.2068607068607069</v>
+      </c>
+      <c r="C12" s="3">
         <v>1.3511652542372883</v>
       </c>
-      <c r="D12" s="5">
-        <v>8.8014377217639744E-2</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" s="4">
+        <v>8.8659508778397303E-2</v>
+      </c>
+      <c r="E12" s="4">
         <v>8.5160126296797478E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
-        <v>1.2029547105836764</v>
-      </c>
-      <c r="C13" s="4">
+      <c r="B13" s="3">
+        <v>1.2035611164581328</v>
+      </c>
+      <c r="C13" s="3">
         <v>1.2147368421052631</v>
       </c>
-      <c r="D13" s="5">
-        <v>9.8527692270980988E-2</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" s="4">
+        <v>9.917197604218865E-2</v>
+      </c>
+      <c r="E13" s="4">
         <v>0.10502111477149616</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
-        <v>1.1980066445182724</v>
-      </c>
-      <c r="C14" s="4">
+      <c r="B14" s="3">
+        <v>1.1973597359735975</v>
+      </c>
+      <c r="C14" s="3">
         <v>1.2427643236857648</v>
       </c>
-      <c r="D14" s="5">
-        <v>8.456481429454403E-2</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="D14" s="4">
+        <v>8.5126706748328368E-2</v>
+      </c>
+      <c r="E14" s="4">
         <v>8.3460685235395612E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1.195099484156227</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.229799723756906</v>
+      </c>
+      <c r="D15" s="4">
+        <v>8.377318887551316E-2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>8.3542478003750184E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="4">
-        <v>1.1953216374269005</v>
-      </c>
-      <c r="C15" s="4">
+      <c r="B16" s="3">
+        <v>1.194923148579413</v>
+      </c>
+      <c r="C16" s="3">
         <v>1.1943195749897833</v>
       </c>
-      <c r="D15" s="5">
-        <v>0.11505853855470327</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="D16" s="4">
+        <v>0.11556990983716862</v>
+      </c>
+      <c r="E16" s="4">
         <v>0.10163859525243504</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4">
-        <v>1.1947955390334573</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1.229799723756906</v>
-      </c>
-      <c r="D16" s="5">
-        <v>8.3032379541315551E-2</v>
-      </c>
-      <c r="E16" s="5">
-        <v>8.3542478003750184E-2</v>
-      </c>
-    </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="4">
-        <v>1.1943385955362003</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B17" s="3">
+        <v>1.1944894651539708</v>
+      </c>
+      <c r="C17" s="3">
         <v>1.2209902011346054</v>
       </c>
-      <c r="D17" s="5">
-        <v>8.2543248708155464E-2</v>
-      </c>
-      <c r="E17" s="5">
+      <c r="D17" s="4">
+        <v>8.3172320826780499E-2</v>
+      </c>
+      <c r="E17" s="4">
         <v>8.3078043659889883E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="4">
-        <v>1.190376018932422</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="B18" s="3">
+        <v>1.1918559122944401</v>
+      </c>
+      <c r="C18" s="3">
         <v>1.201057565196491</v>
       </c>
-      <c r="D18" s="5">
-        <v>0.12524287831384817</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D18" s="4">
+        <v>0.12616499259015312</v>
+      </c>
+      <c r="E18" s="4">
         <v>0.12090083545223393</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4">
-        <v>1.1882166166872465</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="B19" s="3">
+        <v>1.1878065872459704</v>
+      </c>
+      <c r="C19" s="3">
         <v>1.2040006350214318</v>
       </c>
-      <c r="D19" s="5">
-        <v>8.7025267876331705E-2</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" s="4">
+        <v>8.7623959964385489E-2</v>
+      </c>
+      <c r="E19" s="4">
         <v>8.6923522755499125E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4">
-        <v>1.1733793632527809</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="B20" s="3">
+        <v>1.1735978634109119</v>
+      </c>
+      <c r="C20" s="3">
         <v>1.2093946410850147</v>
       </c>
-      <c r="D20" s="5">
-        <v>8.7536095628231822E-2</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D20" s="4">
+        <v>8.8006178228460144E-2</v>
+      </c>
+      <c r="E20" s="4">
         <v>9.2698782619361569E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="7">
-        <v>1.2387917575542835</v>
-      </c>
-      <c r="C21" s="7">
+      <c r="B21" s="5">
+        <v>1.2392745988628491</v>
+      </c>
+      <c r="C21" s="5">
         <v>1.2531976344381792</v>
       </c>
-      <c r="D21" s="8">
-        <v>0.1075180361437177</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="D21" s="6">
+        <v>0.10825138693778423</v>
+      </c>
+      <c r="E21" s="6">
         <v>0.10435572432062265</v>
       </c>
     </row>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFC53E0-F766-4291-A82D-73E0F3029924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023C7A7A-A9DF-445C-9997-91EBB57CA792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,9 +129,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -170,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -178,11 +177,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -190,11 +186,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,342 +554,342 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>1.4166493668258251</v>
-      </c>
-      <c r="C2" s="3">
+      <c r="B2" s="4">
+        <v>1.4153972828324413</v>
+      </c>
+      <c r="C2" s="4">
         <v>1.4160828025477705</v>
       </c>
-      <c r="D2" s="4">
-        <v>0.32975082146768891</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="5">
+        <v>0.33255750273822565</v>
+      </c>
+      <c r="E2" s="5">
         <v>0.13068903086175682</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
-        <v>1.3720637583892616</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="B3" s="4">
+        <v>1.3711554447215295</v>
+      </c>
+      <c r="C3" s="4">
         <v>1.3706164636397193</v>
       </c>
-      <c r="D3" s="4">
-        <v>0.17694648556372003</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3" s="5">
+        <v>0.1785793809841906</v>
+      </c>
+      <c r="E3" s="5">
         <v>0.17533980582524272</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
-        <v>1.3345977240966262</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B4" s="4">
+        <v>1.3361078081648832</v>
+      </c>
+      <c r="C4" s="4">
         <v>1.3269511305616337</v>
       </c>
-      <c r="D4" s="4">
-        <v>0.21868587644619078</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="5">
+        <v>0.2203012442698101</v>
+      </c>
+      <c r="E4" s="5">
         <v>0.20836657927732816</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
-        <v>1.2933206560494415</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="4">
+        <v>1.2925795053003533</v>
+      </c>
+      <c r="C5" s="4">
         <v>1.3297448165869219</v>
       </c>
-      <c r="D5" s="4">
-        <v>8.5351998376952731E-2</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="5">
+        <v>8.6122945830797326E-2</v>
+      </c>
+      <c r="E5" s="5">
         <v>9.792093704245973E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>1.2547658402203856</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="4">
+        <v>1.254521682283722</v>
+      </c>
+      <c r="C6" s="4">
         <v>1.2581814618851657</v>
       </c>
-      <c r="D6" s="4">
-        <v>0.1517583906085386</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="5">
+        <v>0.15348082743858593</v>
+      </c>
+      <c r="E6" s="5">
         <v>0.13729552303056392</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3">
-        <v>1.2343800582712852</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" s="4">
+        <v>1.235096153846154</v>
+      </c>
+      <c r="C7" s="4">
         <v>1.2293759728314702</v>
       </c>
-      <c r="D7" s="4">
-        <v>9.83272588371982E-2</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="5">
+        <v>9.9314032881857681E-2</v>
+      </c>
+      <c r="E7" s="5">
         <v>0.1025868075717106</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
-        <v>1.2304382898628663</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="4">
+        <v>1.2305229455709712</v>
+      </c>
+      <c r="C8" s="4">
         <v>1.2420450482659993</v>
       </c>
-      <c r="D8" s="4">
-        <v>0.11177566722769897</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="5">
+        <v>0.11264727097860062</v>
+      </c>
+      <c r="E8" s="5">
         <v>0.10830031363337163</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
-        <v>1.229112944816916</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" s="4">
+        <v>1.230355771691835</v>
+      </c>
+      <c r="C9" s="4">
         <v>1.2054814597684305</v>
       </c>
-      <c r="D9" s="4">
-        <v>9.9409133438433245E-2</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="5">
+        <v>0.10015252303866908</v>
+      </c>
+      <c r="E9" s="5">
         <v>8.9561838754561446E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
-        <v>1.2260726072607262</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="B10" s="4">
+        <v>1.2262653898768812</v>
+      </c>
+      <c r="C10" s="4">
         <v>1.2619678142187818</v>
       </c>
-      <c r="D10" s="4">
-        <v>6.9374749575470795E-2</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="5">
+        <v>6.9737268893934473E-2</v>
+      </c>
+      <c r="E10" s="5">
         <v>7.4387804582373623E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
-        <v>1.2117578239251243</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="B11" s="4">
+        <v>1.2110304789550073</v>
+      </c>
+      <c r="C11" s="4">
         <v>1.2084191260581101</v>
       </c>
-      <c r="D11" s="4">
-        <v>9.3466375068343363E-2</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="5">
+        <v>9.4177145981410609E-2</v>
+      </c>
+      <c r="E11" s="5">
         <v>9.5474203835568566E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
-        <v>1.2068607068607069</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="B12" s="4">
+        <v>1.2070914696813975</v>
+      </c>
+      <c r="C12" s="4">
         <v>1.3511652542372883</v>
       </c>
-      <c r="D12" s="4">
-        <v>8.8659508778397303E-2</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="D12" s="5">
+        <v>8.9673286945302064E-2</v>
+      </c>
+      <c r="E12" s="5">
         <v>8.5160126296797478E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
-        <v>1.2035611164581328</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B13" s="4">
+        <v>1.2030989272943982</v>
+      </c>
+      <c r="C13" s="4">
         <v>1.2147368421052631</v>
       </c>
-      <c r="D13" s="4">
-        <v>9.917197604218865E-2</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="D13" s="5">
+        <v>0.10010260815615529</v>
+      </c>
+      <c r="E13" s="5">
         <v>0.10502111477149616</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
-        <v>1.1973597359735975</v>
-      </c>
-      <c r="C14" s="3">
+      <c r="B14" s="4">
+        <v>1.1967320261437908</v>
+      </c>
+      <c r="C14" s="4">
         <v>1.2427643236857648</v>
       </c>
-      <c r="D14" s="4">
-        <v>8.5126706748328368E-2</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="D14" s="5">
+        <v>8.5969545429004882E-2</v>
+      </c>
+      <c r="E14" s="5">
         <v>8.3460685235395612E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="3">
-        <v>1.195099484156227</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="B15" s="4">
+        <v>1.1954969796814936</v>
+      </c>
+      <c r="C15" s="4">
         <v>1.229799723756906</v>
       </c>
-      <c r="D15" s="4">
-        <v>8.377318887551316E-2</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="D15" s="5">
+        <v>8.4313362348365589E-2</v>
+      </c>
+      <c r="E15" s="5">
         <v>8.3542478003750184E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="3">
-        <v>1.194923148579413</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="B16" s="4">
+        <v>1.1944444444444444</v>
+      </c>
+      <c r="C16" s="4">
         <v>1.1943195749897833</v>
       </c>
-      <c r="D16" s="4">
-        <v>0.11556990983716862</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D16" s="5">
+        <v>0.11626968106580542</v>
+      </c>
+      <c r="E16" s="5">
         <v>0.10163859525243504</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="3">
-        <v>1.1944894651539708</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B17" s="4">
+        <v>1.1944070986824413</v>
+      </c>
+      <c r="C17" s="4">
         <v>1.2209902011346054</v>
       </c>
-      <c r="D17" s="4">
-        <v>8.3172320826780499E-2</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="D17" s="5">
+        <v>8.3554257470231402E-2</v>
+      </c>
+      <c r="E17" s="5">
         <v>8.3078043659889883E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="3">
-        <v>1.1918559122944401</v>
-      </c>
-      <c r="C18" s="3">
+      <c r="B18" s="4">
+        <v>1.191445236552171</v>
+      </c>
+      <c r="C18" s="4">
         <v>1.201057565196491</v>
       </c>
-      <c r="D18" s="4">
-        <v>0.12616499259015312</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D18" s="5">
+        <v>0.12703770788737032</v>
+      </c>
+      <c r="E18" s="5">
         <v>0.12090083545223393</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
-        <v>1.1878065872459704</v>
-      </c>
-      <c r="C19" s="3">
+      <c r="B19" s="4">
+        <v>1.187239221140473</v>
+      </c>
+      <c r="C19" s="4">
         <v>1.2040006350214318</v>
       </c>
-      <c r="D19" s="4">
-        <v>8.7623959964385489E-2</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="D19" s="5">
+        <v>8.8299407448343623E-2</v>
+      </c>
+      <c r="E19" s="5">
         <v>8.6923522755499125E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
-        <v>1.1735978634109119</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B20" s="4">
+        <v>1.1728301886792454</v>
+      </c>
+      <c r="C20" s="4">
         <v>1.2093946410850147</v>
       </c>
-      <c r="D20" s="4">
-        <v>8.8006178228460144E-2</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="D20" s="5">
+        <v>8.8979920757504535E-2</v>
+      </c>
+      <c r="E20" s="5">
         <v>9.2698782619361569E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5">
-        <v>1.2392745988628491</v>
-      </c>
-      <c r="C21" s="5">
+      <c r="B21" s="6">
+        <v>1.2392525607321676</v>
+      </c>
+      <c r="C21" s="6">
         <v>1.2531976344381792</v>
       </c>
-      <c r="D21" s="6">
-        <v>0.10825138693778423</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="D21" s="7">
+        <v>0.10913712231243601</v>
+      </c>
+      <c r="E21" s="7">
         <v>0.10435572432062265</v>
       </c>
     </row>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023C7A7A-A9DF-445C-9997-91EBB57CA792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4575C4-BFE9-49ED-9B1C-EF25AFCBB3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conv. y Tick" sheetId="3" r:id="rId1"/>
@@ -129,9 +129,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -177,19 +177,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -527,16 +526,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17233115-4901-4354-B5A2-D6FF1650C878}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -553,344 +552,344 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>1.4153972828324413</v>
+        <v>1.4139636075949367</v>
       </c>
       <c r="C2" s="4">
-        <v>1.4160828025477705</v>
+        <v>1.4132687390660745</v>
       </c>
       <c r="D2" s="5">
-        <v>0.33255750273822565</v>
+        <v>0.33056554429552143</v>
       </c>
       <c r="E2" s="5">
-        <v>0.13068903086175682</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.12822238326948959</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1.3711554447215295</v>
+        <v>1.3714867617107944</v>
       </c>
       <c r="C3" s="4">
-        <v>1.3706164636397193</v>
+        <v>1.3646732429099877</v>
       </c>
       <c r="D3" s="5">
-        <v>0.1785793809841906</v>
+        <v>0.17598566308243727</v>
       </c>
       <c r="E3" s="5">
-        <v>0.17533980582524272</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.17409037243747988</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>1.3361078081648832</v>
+        <v>1.3375944218477629</v>
       </c>
       <c r="C4" s="4">
-        <v>1.3269511305616337</v>
+        <v>1.3190447030006125</v>
       </c>
       <c r="D4" s="5">
-        <v>0.2203012442698101</v>
+        <v>0.21866926432594977</v>
       </c>
       <c r="E4" s="5">
-        <v>0.20836657927732816</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.20724665270639001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>1.2925795053003533</v>
+        <v>1.296534312600413</v>
       </c>
       <c r="C5" s="4">
-        <v>1.3297448165869219</v>
+        <v>1.3368037480478916</v>
       </c>
       <c r="D5" s="5">
-        <v>8.6122945830797326E-2</v>
+        <v>8.5449802898664412E-2</v>
       </c>
       <c r="E5" s="5">
-        <v>9.792093704245973E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9.8249143324752375E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>1.254521682283722</v>
+        <v>1.2547878531372343</v>
       </c>
       <c r="C6" s="4">
-        <v>1.2581814618851657</v>
+        <v>1.250354432491035</v>
       </c>
       <c r="D6" s="5">
-        <v>0.15348082743858593</v>
+        <v>0.15804612117259487</v>
       </c>
       <c r="E6" s="5">
-        <v>0.13729552303056392</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.13893909899888765</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="4">
-        <v>1.235096153846154</v>
+        <v>1.2347241756524456</v>
       </c>
       <c r="C7" s="4">
-        <v>1.2293759728314702</v>
+        <v>1.2246970994982256</v>
       </c>
       <c r="D7" s="5">
-        <v>9.9314032881857681E-2</v>
+        <v>0.10000156276860085</v>
       </c>
       <c r="E7" s="5">
-        <v>0.1025868075717106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.10209538565341797</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>1.2305229455709712</v>
+        <v>1.2305408545243319</v>
       </c>
       <c r="C8" s="4">
-        <v>1.2420450482659993</v>
+        <v>1.2383614555804026</v>
       </c>
       <c r="D8" s="5">
-        <v>0.11264727097860062</v>
+        <v>0.11223794966895093</v>
       </c>
       <c r="E8" s="5">
-        <v>0.10830031363337163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.1095618860948393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>1.230355771691835</v>
+        <v>1.2299465240641712</v>
       </c>
       <c r="C9" s="4">
-        <v>1.2054814597684305</v>
+        <v>1.2016724053123464</v>
       </c>
       <c r="D9" s="5">
-        <v>0.10015252303866908</v>
+        <v>9.9627064464571119E-2</v>
       </c>
       <c r="E9" s="5">
-        <v>8.9561838754561446E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9.078223204617257E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>1.2262653898768812</v>
+        <v>1.2260526315789473</v>
       </c>
       <c r="C10" s="4">
-        <v>1.2619678142187818</v>
+        <v>1.2763180789977377</v>
       </c>
       <c r="D10" s="5">
-        <v>6.9737268893934473E-2</v>
+        <v>7.000221059612409E-2</v>
       </c>
       <c r="E10" s="5">
-        <v>7.4387804582373623E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>7.4241054127373723E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>1.2110304789550073</v>
+        <v>1.2109419063733784</v>
       </c>
       <c r="C11" s="4">
-        <v>1.2084191260581101</v>
+        <v>1.2127823904228616</v>
       </c>
       <c r="D11" s="5">
-        <v>9.4177145981410609E-2</v>
+        <v>9.3680650956356332E-2</v>
       </c>
       <c r="E11" s="5">
-        <v>9.5474203835568566E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9.5866575347537161E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="4">
-        <v>1.2070914696813975</v>
+        <v>1.2081673306772909</v>
       </c>
       <c r="C12" s="4">
-        <v>1.3511652542372883</v>
+        <v>1.3470031545741326</v>
       </c>
       <c r="D12" s="5">
-        <v>8.9673286945302064E-2</v>
+        <v>8.8645594208016959E-2</v>
       </c>
       <c r="E12" s="5">
-        <v>8.5160126296797478E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8.6934378060724779E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="4">
-        <v>1.2030989272943982</v>
+        <v>1.2024085224641037</v>
       </c>
       <c r="C13" s="4">
-        <v>1.2147368421052631</v>
+        <v>1.2116212338593972</v>
       </c>
       <c r="D13" s="5">
-        <v>0.10010260815615529</v>
+        <v>9.9692932837716158E-2</v>
       </c>
       <c r="E13" s="5">
-        <v>0.10502111477149616</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.10471361502347418</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>1.1967320261437908</v>
+        <v>1.2012738853503184</v>
       </c>
       <c r="C14" s="4">
-        <v>1.2427643236857648</v>
+        <v>1.2359897172236505</v>
       </c>
       <c r="D14" s="5">
-        <v>8.5969545429004882E-2</v>
+        <v>8.5228814939471251E-2</v>
       </c>
       <c r="E14" s="5">
-        <v>8.3460685235395612E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8.3397650287282396E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="4">
-        <v>1.1954969796814936</v>
+        <v>1.195966446546493</v>
       </c>
       <c r="C15" s="4">
-        <v>1.229799723756906</v>
+        <v>1.2233621574087645</v>
       </c>
       <c r="D15" s="5">
-        <v>8.4313362348365589E-2</v>
+        <v>8.4684793615767126E-2</v>
       </c>
       <c r="E15" s="5">
-        <v>8.3542478003750184E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8.4055042932994956E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1.1949882537196554</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1.2135922330097089</v>
+      </c>
+      <c r="D16" s="5">
+        <v>8.3033508171138762E-2</v>
+      </c>
+      <c r="E16" s="5">
+        <v>8.3290849960446514E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="4">
-        <v>1.1944444444444444</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1.1943195749897833</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.11626968106580542</v>
-      </c>
-      <c r="E16" s="5">
-        <v>0.10163859525243504</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="B17" s="4">
-        <v>1.1944070986824413</v>
+        <v>1.194262480234922</v>
       </c>
       <c r="C17" s="4">
-        <v>1.2209902011346054</v>
+        <v>1.1883519206939281</v>
       </c>
       <c r="D17" s="5">
-        <v>8.3554257470231402E-2</v>
+        <v>0.11555126331175611</v>
       </c>
       <c r="E17" s="5">
-        <v>8.3078043659889883E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.10099402867665463</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="4">
-        <v>1.191445236552171</v>
+        <v>1.1922785768357305</v>
       </c>
       <c r="C18" s="4">
-        <v>1.201057565196491</v>
+        <v>1.201725012683917</v>
       </c>
       <c r="D18" s="5">
-        <v>0.12703770788737032</v>
+        <v>0.12628861872819108</v>
       </c>
       <c r="E18" s="5">
-        <v>0.12090083545223393</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>0.12195423777054536</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="4">
-        <v>1.187239221140473</v>
+        <v>1.1843650394229155</v>
       </c>
       <c r="C19" s="4">
-        <v>1.2040006350214318</v>
+        <v>1.1988727858293076</v>
       </c>
       <c r="D19" s="5">
-        <v>8.8299407448343623E-2</v>
+        <v>8.8578815977175457E-2</v>
       </c>
       <c r="E19" s="5">
-        <v>8.6923522755499125E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8.7093720416535181E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="4">
-        <v>1.1728301886792454</v>
+        <v>1.1803519061583576</v>
       </c>
       <c r="C20" s="4">
-        <v>1.2093946410850147</v>
+        <v>1.2026419336706016</v>
       </c>
       <c r="D20" s="5">
-        <v>8.8979920757504535E-2</v>
+        <v>8.8090932575561873E-2</v>
       </c>
       <c r="E20" s="5">
-        <v>9.2698782619361569E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+        <v>9.2934569674807371E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="6">
-        <v>1.2392525607321676</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1.2531976344381792</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.10913712231243601</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.10435572432062265</v>
+      <c r="B21" s="7">
+        <v>1.2396516469429053</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1.2502607578248208</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.10905147961877561</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.10469837941728913</v>
       </c>
     </row>
   </sheetData>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4575C4-BFE9-49ED-9B1C-EF25AFCBB3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E96005-4384-4084-BC7B-794F8BA5495C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conv. y Tick" sheetId="3" r:id="rId1"/>
@@ -132,6 +132,7 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -177,19 +178,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,16 +531,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17233115-4901-4354-B5A2-D6FF1650C878}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,343 +557,343 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>1.4139636075949367</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2" s="3">
+        <v>1.4113667117726656</v>
+      </c>
+      <c r="C2" s="3">
         <v>1.4132687390660745</v>
       </c>
-      <c r="D2" s="5">
-        <v>0.33056554429552143</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="4">
+        <v>0.32184408635600076</v>
+      </c>
+      <c r="E2" s="4">
         <v>0.12822238326948959</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
-        <v>1.3714867617107944</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="3">
+        <v>1.3694779116465863</v>
+      </c>
+      <c r="C3" s="3">
         <v>1.3646732429099877</v>
       </c>
-      <c r="D3" s="5">
-        <v>0.17598566308243727</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3" s="4">
+        <v>0.17328972092699563</v>
+      </c>
+      <c r="E3" s="4">
         <v>0.17409037243747988</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>1.3375944218477629</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>1.3190447030006125</v>
       </c>
-      <c r="D4" s="5">
-        <v>0.21866926432594977</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="4">
+        <v>0.2148474886604802</v>
+      </c>
+      <c r="E4" s="4">
         <v>0.20724665270639001</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
-        <v>1.296534312600413</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="B5" s="3">
+        <v>1.2972241029113067</v>
+      </c>
+      <c r="C5" s="3">
         <v>1.3368037480478916</v>
       </c>
-      <c r="D5" s="5">
-        <v>8.5449802898664412E-2</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="4">
+        <v>8.4433773509403759E-2</v>
+      </c>
+      <c r="E5" s="4">
         <v>9.8249143324752375E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>1.2547878531372343</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="B6" s="3">
+        <v>1.254579517069109</v>
+      </c>
+      <c r="C6" s="3">
         <v>1.250354432491035</v>
       </c>
-      <c r="D6" s="5">
-        <v>0.15804612117259487</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6" s="4">
+        <v>0.16067158313684177</v>
+      </c>
+      <c r="E6" s="4">
         <v>0.13893909899888765</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4">
-        <v>1.2347241756524456</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="3">
+        <v>1.2340686274509804</v>
+      </c>
+      <c r="C7" s="3">
         <v>1.2246970994982256</v>
       </c>
-      <c r="D7" s="5">
-        <v>0.10000156276860085</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" s="4">
+        <v>9.7264437689969604E-2</v>
+      </c>
+      <c r="E7" s="4">
         <v>0.10209538565341797</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
-        <v>1.2305408545243319</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="B8" s="3">
+        <v>1.2304677623261695</v>
+      </c>
+      <c r="C8" s="3">
         <v>1.2383614555804026</v>
       </c>
-      <c r="D8" s="5">
-        <v>0.11223794966895093</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="4">
+        <v>0.11056751467710371</v>
+      </c>
+      <c r="E8" s="4">
         <v>0.1095618860948393</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
-        <v>1.2299465240641712</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="B9" s="3">
+        <v>1.2301596976715836</v>
+      </c>
+      <c r="C9" s="3">
         <v>1.2016724053123464</v>
       </c>
-      <c r="D9" s="5">
-        <v>9.9627064464571119E-2</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" s="4">
+        <v>9.8464751707498591E-2</v>
+      </c>
+      <c r="E9" s="4">
         <v>9.078223204617257E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
-        <v>1.2260526315789473</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="B10" s="3">
+        <v>1.2249037227214377</v>
+      </c>
+      <c r="C10" s="3">
         <v>1.2763180789977377</v>
       </c>
-      <c r="D10" s="5">
-        <v>7.000221059612409E-2</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="4">
+        <v>6.923090595616857E-2</v>
+      </c>
+      <c r="E10" s="4">
         <v>7.4241054127373723E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
-        <v>1.2109419063733784</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="B11" s="3">
+        <v>1.2124896380215529</v>
+      </c>
+      <c r="C11" s="3">
         <v>1.2127823904228616</v>
       </c>
-      <c r="D11" s="5">
-        <v>9.3680650956356332E-2</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="4">
+        <v>9.2326139088729012E-2</v>
+      </c>
+      <c r="E11" s="4">
         <v>9.5866575347537161E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
-        <v>1.2081673306772909</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="B12" s="3">
+        <v>1.2071323888617489</v>
+      </c>
+      <c r="C12" s="3">
         <v>1.3470031545741326</v>
       </c>
-      <c r="D12" s="5">
-        <v>8.8645594208016959E-2</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" s="4">
+        <v>8.722887458984957E-2</v>
+      </c>
+      <c r="E12" s="4">
         <v>8.6934378060724779E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
-        <v>1.2024085224641037</v>
-      </c>
-      <c r="C13" s="4">
+      <c r="B13" s="3">
+        <v>1.2020018198362148</v>
+      </c>
+      <c r="C13" s="3">
         <v>1.2116212338593972</v>
       </c>
-      <c r="D13" s="5">
-        <v>9.9692932837716158E-2</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" s="4">
+        <v>9.8403957647796206E-2</v>
+      </c>
+      <c r="E13" s="4">
         <v>0.10471361502347418</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
-        <v>1.2012738853503184</v>
-      </c>
-      <c r="C14" s="4">
+      <c r="B14" s="3">
+        <v>1.2006230529595017</v>
+      </c>
+      <c r="C14" s="3">
         <v>1.2359897172236505</v>
       </c>
-      <c r="D14" s="5">
-        <v>8.5228814939471251E-2</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="D14" s="4">
+        <v>8.4327221142226655E-2</v>
+      </c>
+      <c r="E14" s="4">
         <v>8.3397650287282396E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="4">
-        <v>1.195966446546493</v>
-      </c>
-      <c r="C15" s="4">
+      <c r="B15" s="3">
+        <v>1.1972693856117627</v>
+      </c>
+      <c r="C15" s="3">
         <v>1.2233621574087645</v>
       </c>
-      <c r="D15" s="5">
-        <v>8.4684793615767126E-2</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="D15" s="4">
+        <v>8.4964306960142774E-2</v>
+      </c>
+      <c r="E15" s="4">
         <v>8.4055042932994956E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="4">
-        <v>1.1949882537196554</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="B16" s="3">
+        <v>1.1957468613886753</v>
+      </c>
+      <c r="C16" s="3">
         <v>1.2135922330097089</v>
       </c>
-      <c r="D16" s="5">
-        <v>8.3033508171138762E-2</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="D16" s="4">
+        <v>8.1569102802566407E-2</v>
+      </c>
+      <c r="E16" s="4">
         <v>8.3290849960446514E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1.1937639198218262</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.201725012683917</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.12450318883445789</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0.12195423777054536</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4">
-        <v>1.194262480234922</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B18" s="3">
+        <v>1.1934768138451297</v>
+      </c>
+      <c r="C18" s="3">
         <v>1.1883519206939281</v>
       </c>
-      <c r="D17" s="5">
-        <v>0.11555126331175611</v>
-      </c>
-      <c r="E17" s="5">
+      <c r="D18" s="4">
+        <v>0.11358366935483871</v>
+      </c>
+      <c r="E18" s="4">
         <v>0.10099402867665463</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4">
-        <v>1.1922785768357305</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1.201725012683917</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.12628861872819108</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0.12195423777054536</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4">
-        <v>1.1843650394229155</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="B19" s="3">
+        <v>1.1840591618734593</v>
+      </c>
+      <c r="C19" s="3">
         <v>1.1988727858293076</v>
       </c>
-      <c r="D19" s="5">
-        <v>8.8578815977175457E-2</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" s="4">
+        <v>8.7156423220705562E-2</v>
+      </c>
+      <c r="E19" s="4">
         <v>8.7093720416535181E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4">
-        <v>1.1803519061583576</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="B20" s="3">
+        <v>1.1827648114901257</v>
+      </c>
+      <c r="C20" s="3">
         <v>1.2026419336706016</v>
       </c>
-      <c r="D20" s="5">
-        <v>8.8090932575561873E-2</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="D20" s="4">
+        <v>8.6708801643886793E-2</v>
+      </c>
+      <c r="E20" s="4">
         <v>9.2934569674807371E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="7">
-        <v>1.2396516469429053</v>
-      </c>
-      <c r="C21" s="7">
+      <c r="B21" s="5">
+        <v>1.2395390200014562</v>
+      </c>
+      <c r="C21" s="5">
         <v>1.2502607578248208</v>
       </c>
-      <c r="D21" s="8">
-        <v>0.10905147961877561</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="D21" s="6">
+        <v>0.10766691266306594</v>
+      </c>
+      <c r="E21" s="6">
         <v>0.10469837941728913</v>
       </c>
     </row>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E96005-4384-4084-BC7B-794F8BA5495C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6F6864-7B79-4B7D-BB0F-1BFB830C5D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,7 +132,6 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -184,17 +183,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,7 +534,7 @@
   <cols>
     <col min="1" max="1" width="24.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
@@ -558,342 +557,342 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4113667117726656</v>
+        <v>1.4099271751628975</v>
       </c>
       <c r="C2" s="3">
         <v>1.4132687390660745</v>
       </c>
       <c r="D2" s="4">
-        <v>0.32184408635600076</v>
+        <v>0.32464381260498976</v>
       </c>
       <c r="E2" s="4">
         <v>0.12822238326948959</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3694779116465863</v>
+        <v>1.3685464654487689</v>
       </c>
       <c r="C3" s="3">
         <v>1.3646732429099877</v>
       </c>
       <c r="D3" s="4">
-        <v>0.17328972092699563</v>
+        <v>0.17523836035910642</v>
       </c>
       <c r="E3" s="4">
         <v>0.17409037243747988</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3375944218477629</v>
+        <v>1.3359728506787329</v>
       </c>
       <c r="C4" s="3">
         <v>1.3190447030006125</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2148474886604802</v>
+        <v>0.22071490990803547</v>
       </c>
       <c r="E4" s="4">
         <v>0.20724665270639001</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2972241029113067</v>
+        <v>1.2992602555480834</v>
       </c>
       <c r="C5" s="3">
         <v>1.3368037480478916</v>
       </c>
       <c r="D5" s="4">
-        <v>8.4433773509403759E-2</v>
+        <v>8.500543074372606E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.8249143324752375E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.254579517069109</v>
+        <v>1.2536665978103698</v>
       </c>
       <c r="C6" s="3">
         <v>1.250354432491035</v>
       </c>
       <c r="D6" s="4">
-        <v>0.16067158313684177</v>
+        <v>0.16190906202444857</v>
       </c>
       <c r="E6" s="4">
         <v>0.13893909899888765</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2340686274509804</v>
+        <v>1.2331362740639684</v>
       </c>
       <c r="C7" s="3">
         <v>1.2246970994982256</v>
       </c>
       <c r="D7" s="4">
-        <v>9.7264437689969604E-2</v>
+        <v>9.8292508492758807E-2</v>
       </c>
       <c r="E7" s="4">
         <v>0.10209538565341797</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2304677623261695</v>
+        <v>1.230605071554105</v>
       </c>
       <c r="C8" s="3">
         <v>1.2383614555804026</v>
       </c>
       <c r="D8" s="4">
-        <v>0.11056751467710371</v>
+        <v>0.11135029354207436</v>
       </c>
       <c r="E8" s="4">
         <v>0.1095618860948393</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2301596976715836</v>
+        <v>1.2297526673132881</v>
       </c>
       <c r="C9" s="3">
         <v>1.2016724053123464</v>
       </c>
       <c r="D9" s="4">
-        <v>9.8464751707498591E-2</v>
+        <v>9.9004909433554597E-2</v>
       </c>
       <c r="E9" s="4">
         <v>9.078223204617257E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2249037227214377</v>
+        <v>1.2245676500508647</v>
       </c>
       <c r="C10" s="3">
         <v>1.2763180789977377</v>
       </c>
       <c r="D10" s="4">
-        <v>6.923090595616857E-2</v>
+        <v>6.988855512699739E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.4241054127373723E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2124896380215529</v>
+        <v>1.211755012359242</v>
       </c>
       <c r="C11" s="3">
         <v>1.2127823904228616</v>
       </c>
       <c r="D11" s="4">
-        <v>9.2326139088729012E-2</v>
+        <v>9.2887392213888462E-2</v>
       </c>
       <c r="E11" s="4">
         <v>9.5866575347537161E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2071323888617489</v>
+        <v>1.2058111380145278</v>
       </c>
       <c r="C12" s="3">
         <v>1.3470031545741326</v>
       </c>
       <c r="D12" s="4">
-        <v>8.722887458984957E-2</v>
+        <v>8.7995909149017768E-2</v>
       </c>
       <c r="E12" s="4">
         <v>8.6934378060724779E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2020018198362148</v>
+        <v>1.2022573363431153</v>
       </c>
       <c r="C13" s="3">
         <v>1.2116212338593972</v>
       </c>
       <c r="D13" s="4">
-        <v>9.8403957647796206E-2</v>
+        <v>9.9165043762451596E-2</v>
       </c>
       <c r="E13" s="4">
         <v>0.10471361502347418</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1.2006230529595017</v>
+        <v>1.1997518610421836</v>
       </c>
       <c r="C14" s="3">
         <v>1.2359897172236505</v>
       </c>
       <c r="D14" s="4">
-        <v>8.4327221142226655E-2</v>
+        <v>8.4695003415121109E-2</v>
       </c>
       <c r="E14" s="4">
         <v>8.3397650287282396E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1972693856117627</v>
+        <v>1.1960716148096646</v>
       </c>
       <c r="C15" s="3">
         <v>1.2233621574087645</v>
       </c>
       <c r="D15" s="4">
-        <v>8.4964306960142774E-2</v>
+        <v>8.5559190957763237E-2</v>
       </c>
       <c r="E15" s="4">
         <v>8.4055042932994956E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1957468613886753</v>
+        <v>1.1957186544342508</v>
       </c>
       <c r="C16" s="3">
         <v>1.2135922330097089</v>
       </c>
       <c r="D16" s="4">
-        <v>8.1569102802566407E-2</v>
+        <v>8.200798344792995E-2</v>
       </c>
       <c r="E16" s="4">
         <v>8.3290849960446514E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1.1938685487428318</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.1883519206939281</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.1142641129032258</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0.10099402867665463</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="3">
-        <v>1.1937639198218262</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B18" s="3">
+        <v>1.1935721295387636</v>
+      </c>
+      <c r="C18" s="3">
         <v>1.201725012683917</v>
       </c>
-      <c r="D17" s="4">
-        <v>0.12450318883445789</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="D18" s="4">
+        <v>0.12558153865113844</v>
+      </c>
+      <c r="E18" s="4">
         <v>0.12195423777054536</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3">
-        <v>1.1934768138451297</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1.1883519206939281</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0.11358366935483871</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0.10099402867665463</v>
-      </c>
-    </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1840591618734593</v>
+        <v>1.1845402766476809</v>
       </c>
       <c r="C19" s="3">
         <v>1.1988727858293076</v>
       </c>
       <c r="D19" s="4">
-        <v>8.7156423220705562E-2</v>
+        <v>8.8015812767664042E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.7093720416535181E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1827648114901257</v>
+        <v>1.1828225231646472</v>
       </c>
       <c r="C20" s="3">
         <v>1.2026419336706016</v>
       </c>
       <c r="D20" s="4">
-        <v>8.6708801643886793E-2</v>
+        <v>8.7362620255923285E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.2934569674807371E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5">
-        <v>1.2395390200014562</v>
-      </c>
-      <c r="C21" s="5">
+      <c r="B21" s="7">
+        <v>1.2392770239617272</v>
+      </c>
+      <c r="C21" s="7">
         <v>1.2502607578248208</v>
       </c>
-      <c r="D21" s="6">
-        <v>0.10766691266306594</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="D21" s="8">
+        <v>0.10861319623233558</v>
+      </c>
+      <c r="E21" s="8">
         <v>0.10469837941728913</v>
       </c>
     </row>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6F6864-7B79-4B7D-BB0F-1BFB830C5D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08132122-0E4C-42A3-B9E6-FD1074600B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4099271751628975</v>
+        <v>1.4081976417742841</v>
       </c>
       <c r="C2" s="3">
         <v>1.4132687390660745</v>
       </c>
       <c r="D2" s="4">
-        <v>0.32464381260498976</v>
+        <v>0.33242082996329247</v>
       </c>
       <c r="E2" s="4">
         <v>0.12822238326948959</v>
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3685464654487689</v>
+        <v>1.368380062305296</v>
       </c>
       <c r="C3" s="3">
         <v>1.3646732429099877</v>
       </c>
       <c r="D3" s="4">
-        <v>0.17523836035910642</v>
+        <v>0.17871807363073283</v>
       </c>
       <c r="E3" s="4">
         <v>0.17409037243747988</v>
@@ -595,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3359728506787329</v>
+        <v>1.3357287635894601</v>
       </c>
       <c r="C4" s="3">
         <v>1.3190447030006125</v>
       </c>
       <c r="D4" s="4">
-        <v>0.22071490990803547</v>
+        <v>0.22583329865590279</v>
       </c>
       <c r="E4" s="4">
         <v>0.20724665270639001</v>
@@ -612,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2992602555480834</v>
+        <v>1.3001100110011001</v>
       </c>
       <c r="C5" s="3">
         <v>1.3368037480478916</v>
       </c>
       <c r="D5" s="4">
-        <v>8.500543074372606E-2</v>
+        <v>8.6606070999828505E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.8249143324752375E-2</v>
@@ -629,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2536665978103698</v>
+        <v>1.2540343042728104</v>
       </c>
       <c r="C6" s="3">
         <v>1.250354432491035</v>
       </c>
       <c r="D6" s="4">
-        <v>0.16190906202444857</v>
+        <v>0.16476864161608054</v>
       </c>
       <c r="E6" s="4">
         <v>0.13893909899888765</v>
@@ -646,13 +646,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2331362740639684</v>
+        <v>1.2332443653618033</v>
       </c>
       <c r="C7" s="3">
         <v>1.2246970994982256</v>
       </c>
       <c r="D7" s="4">
-        <v>9.8292508492758807E-2</v>
+        <v>0.10048274629000536</v>
       </c>
       <c r="E7" s="4">
         <v>0.10209538565341797</v>
@@ -663,13 +663,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1.230605071554105</v>
+        <v>1.2300036859565058</v>
       </c>
       <c r="C8" s="3">
         <v>1.2383614555804026</v>
       </c>
       <c r="D8" s="4">
-        <v>0.11135029354207436</v>
+        <v>0.11376852110707297</v>
       </c>
       <c r="E8" s="4">
         <v>0.1095618860948393</v>
@@ -680,13 +680,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2297526673132881</v>
+        <v>1.2294243577545194</v>
       </c>
       <c r="C9" s="3">
         <v>1.2016724053123464</v>
       </c>
       <c r="D9" s="4">
-        <v>9.9004909433554597E-2</v>
+        <v>0.1009254702373093</v>
       </c>
       <c r="E9" s="4">
         <v>9.078223204617257E-2</v>
@@ -697,13 +697,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2245676500508647</v>
+        <v>1.2260631683660781</v>
       </c>
       <c r="C10" s="3">
         <v>1.2763180789977377</v>
       </c>
       <c r="D10" s="4">
-        <v>6.988855512699739E-2</v>
+        <v>7.1470467997369405E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.4241054127373723E-2</v>
@@ -714,13 +714,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.211755012359242</v>
+        <v>1.2107659346545259</v>
       </c>
       <c r="C11" s="3">
         <v>1.2127823904228616</v>
       </c>
       <c r="D11" s="4">
-        <v>9.2887392213888462E-2</v>
+        <v>9.5259962242971577E-2</v>
       </c>
       <c r="E11" s="4">
         <v>9.5866575347537161E-2</v>
@@ -731,13 +731,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2058111380145278</v>
+        <v>1.2037037037037039</v>
       </c>
       <c r="C12" s="3">
         <v>1.3470031545741326</v>
       </c>
       <c r="D12" s="4">
-        <v>8.7995909149017768E-2</v>
+        <v>8.9743043422678651E-2</v>
       </c>
       <c r="E12" s="4">
         <v>8.6934378060724779E-2</v>
@@ -748,13 +748,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2022573363431153</v>
+        <v>1.2030837004405286</v>
       </c>
       <c r="C13" s="3">
         <v>1.2116212338593972</v>
       </c>
       <c r="D13" s="4">
-        <v>9.9165043762451596E-2</v>
+        <v>0.10162738119221901</v>
       </c>
       <c r="E13" s="4">
         <v>0.10471361502347418</v>
@@ -765,13 +765,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1.1997518610421836</v>
+        <v>1.1984175289105294</v>
       </c>
       <c r="C14" s="3">
         <v>1.2359897172236505</v>
       </c>
       <c r="D14" s="4">
-        <v>8.4695003415121109E-2</v>
+        <v>8.6323753480796517E-2</v>
       </c>
       <c r="E14" s="4">
         <v>8.3397650287282396E-2</v>
@@ -782,13 +782,13 @@
         <v>15</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1960716148096646</v>
+        <v>1.1960416311209692</v>
       </c>
       <c r="C15" s="3">
         <v>1.2233621574087645</v>
       </c>
       <c r="D15" s="4">
-        <v>8.5559190957763237E-2</v>
+        <v>8.7165377751338494E-2</v>
       </c>
       <c r="E15" s="4">
         <v>8.4055042932994956E-2</v>
@@ -799,13 +799,13 @@
         <v>17</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1957186544342508</v>
+        <v>1.194853859605296</v>
       </c>
       <c r="C16" s="3">
         <v>1.2135922330097089</v>
       </c>
       <c r="D16" s="4">
-        <v>8.200798344792995E-2</v>
+        <v>8.3659010637630885E-2</v>
       </c>
       <c r="E16" s="4">
         <v>8.3290849960446514E-2</v>
@@ -813,36 +813,36 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1938685487428318</v>
+        <v>1.1933933933933936</v>
       </c>
       <c r="C17" s="3">
-        <v>1.1883519206939281</v>
+        <v>1.201725012683917</v>
       </c>
       <c r="D17" s="4">
-        <v>0.1142641129032258</v>
+        <v>0.12824660319807746</v>
       </c>
       <c r="E17" s="4">
-        <v>0.10099402867665463</v>
+        <v>0.12195423777054536</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1935721295387636</v>
+        <v>1.1929406669553919</v>
       </c>
       <c r="C18" s="3">
-        <v>1.201725012683917</v>
+        <v>1.1883519206939281</v>
       </c>
       <c r="D18" s="4">
-        <v>0.12558153865113844</v>
+        <v>0.11638104838709677</v>
       </c>
       <c r="E18" s="4">
-        <v>0.12195423777054536</v>
+        <v>0.10099402867665463</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1845402766476809</v>
+        <v>1.1849152273807637</v>
       </c>
       <c r="C19" s="3">
         <v>1.1988727858293076</v>
       </c>
       <c r="D19" s="4">
-        <v>8.8015812767664042E-2</v>
+        <v>9.039345718091582E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.7093720416535181E-2</v>
@@ -867,13 +867,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1828225231646472</v>
+        <v>1.1814698711250435</v>
       </c>
       <c r="C20" s="3">
         <v>1.2026419336706016</v>
       </c>
       <c r="D20" s="4">
-        <v>8.7362620255923285E-2</v>
+        <v>8.9386344531274323E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.2934569674807371E-2</v>
@@ -884,13 +884,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2392770239617272</v>
+        <v>1.2390571370886332</v>
       </c>
       <c r="C21" s="7">
         <v>1.2502607578248208</v>
       </c>
       <c r="D21" s="8">
-        <v>0.10861319623233558</v>
+        <v>0.11093355073591746</v>
       </c>
       <c r="E21" s="8">
         <v>0.10469837941728913</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08132122-0E4C-42A3-B9E6-FD1074600B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0917B532-B9E4-4E94-827C-6797546EDB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4081976417742841</v>
+        <v>1.4060807268914903</v>
       </c>
       <c r="C2" s="3">
         <v>1.4132687390660745</v>
       </c>
       <c r="D2" s="4">
-        <v>0.33242082996329247</v>
+        <v>0.32555890551225897</v>
       </c>
       <c r="E2" s="4">
         <v>0.12822238326948959</v>
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.368380062305296</v>
+        <v>1.3670289855072464</v>
       </c>
       <c r="C3" s="3">
         <v>1.3646732429099877</v>
       </c>
       <c r="D3" s="4">
-        <v>0.17871807363073283</v>
+        <v>0.1758970110254286</v>
       </c>
       <c r="E3" s="4">
         <v>0.17409037243747988</v>
@@ -595,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3357287635894601</v>
+        <v>1.3313650573115665</v>
       </c>
       <c r="C4" s="3">
         <v>1.3190447030006125</v>
       </c>
       <c r="D4" s="4">
-        <v>0.22583329865590279</v>
+        <v>0.21893536121673005</v>
       </c>
       <c r="E4" s="4">
         <v>0.20724665270639001</v>
@@ -612,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.3001100110011001</v>
+        <v>1.2976114986260832</v>
       </c>
       <c r="C5" s="3">
         <v>1.3368037480478916</v>
       </c>
       <c r="D5" s="4">
-        <v>8.6606070999828505E-2</v>
+        <v>8.4355609442978388E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.8249143324752375E-2</v>
@@ -629,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2540343042728104</v>
+        <v>1.2520096852300242</v>
       </c>
       <c r="C6" s="3">
         <v>1.250354432491035</v>
       </c>
       <c r="D6" s="4">
-        <v>0.16476864161608054</v>
+        <v>0.17266175019649158</v>
       </c>
       <c r="E6" s="4">
         <v>0.13893909899888765</v>
@@ -646,13 +646,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2332443653618033</v>
+        <v>1.2322834645669292</v>
       </c>
       <c r="C7" s="3">
         <v>1.2246970994982256</v>
       </c>
       <c r="D7" s="4">
-        <v>0.10048274629000536</v>
+        <v>9.8465968876336046E-2</v>
       </c>
       <c r="E7" s="4">
         <v>0.10209538565341797</v>
@@ -660,36 +660,36 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2300036859565058</v>
+        <v>1.2287463160281114</v>
       </c>
       <c r="C8" s="3">
-        <v>1.2383614555804026</v>
+        <v>1.2016724053123464</v>
       </c>
       <c r="D8" s="4">
-        <v>0.11376852110707297</v>
+        <v>9.9203850305865413E-2</v>
       </c>
       <c r="E8" s="4">
-        <v>0.1095618860948393</v>
+        <v>9.078223204617257E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2294243577545194</v>
+        <v>1.2283757111343319</v>
       </c>
       <c r="C9" s="3">
-        <v>1.2016724053123464</v>
+        <v>1.2383614555804026</v>
       </c>
       <c r="D9" s="4">
-        <v>0.1009254702373093</v>
+        <v>0.11217034577065833</v>
       </c>
       <c r="E9" s="4">
-        <v>9.078223204617257E-2</v>
+        <v>0.1095618860948393</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -697,13 +697,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2260631683660781</v>
+        <v>1.2246768507638073</v>
       </c>
       <c r="C10" s="3">
         <v>1.2763180789977377</v>
       </c>
       <c r="D10" s="4">
-        <v>7.1470467997369405E-2</v>
+        <v>6.9784986797434931E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.4241054127373723E-2</v>
@@ -714,13 +714,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2107659346545259</v>
+        <v>1.210910005027652</v>
       </c>
       <c r="C11" s="3">
         <v>1.2127823904228616</v>
       </c>
       <c r="D11" s="4">
-        <v>9.5259962242971577E-2</v>
+        <v>9.334303212333106E-2</v>
       </c>
       <c r="E11" s="4">
         <v>9.5866575347537161E-2</v>
@@ -731,13 +731,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2037037037037039</v>
+        <v>1.2081081081081082</v>
       </c>
       <c r="C12" s="3">
         <v>1.3470031545741326</v>
       </c>
       <c r="D12" s="4">
-        <v>8.9743043422678651E-2</v>
+        <v>8.8442691526234019E-2</v>
       </c>
       <c r="E12" s="4">
         <v>8.6934378060724779E-2</v>
@@ -748,13 +748,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2030837004405286</v>
+        <v>1.2030723905723906</v>
       </c>
       <c r="C13" s="3">
         <v>1.2116212338593972</v>
       </c>
       <c r="D13" s="4">
-        <v>0.10162738119221901</v>
+        <v>9.8835274542429283E-2</v>
       </c>
       <c r="E13" s="4">
         <v>0.10471361502347418</v>
@@ -765,13 +765,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1.1984175289105294</v>
+        <v>1.1961471103327495</v>
       </c>
       <c r="C14" s="3">
         <v>1.2359897172236505</v>
       </c>
       <c r="D14" s="4">
-        <v>8.6323753480796517E-2</v>
+        <v>8.4580062213005486E-2</v>
       </c>
       <c r="E14" s="4">
         <v>8.3397650287282396E-2</v>
@@ -779,70 +779,70 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1960416311209692</v>
+        <v>1.1942421483841603</v>
       </c>
       <c r="C15" s="3">
-        <v>1.2233621574087645</v>
+        <v>1.201725012683917</v>
       </c>
       <c r="D15" s="4">
-        <v>8.7165377751338494E-2</v>
+        <v>0.12548370054117344</v>
       </c>
       <c r="E15" s="4">
-        <v>8.4055042932994956E-2</v>
+        <v>0.12195423777054536</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>1.194853859605296</v>
+        <v>1.1921955958549224</v>
       </c>
       <c r="C16" s="3">
-        <v>1.2135922330097089</v>
+        <v>1.2233621574087645</v>
       </c>
       <c r="D16" s="4">
-        <v>8.3659010637630885E-2</v>
+        <v>8.7523383028173002E-2</v>
       </c>
       <c r="E16" s="4">
-        <v>8.3290849960446514E-2</v>
+        <v>8.4055042932994956E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1933933933933936</v>
+        <v>1.1921884686918784</v>
       </c>
       <c r="C17" s="3">
-        <v>1.201725012683917</v>
+        <v>1.1883519206939281</v>
       </c>
       <c r="D17" s="4">
-        <v>0.12824660319807746</v>
+        <v>0.11342115132195763</v>
       </c>
       <c r="E17" s="4">
-        <v>0.12195423777054536</v>
+        <v>0.10099402867665463</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1929406669553919</v>
+        <v>1.1912491178546225</v>
       </c>
       <c r="C18" s="3">
-        <v>1.1883519206939281</v>
+        <v>1.2135922330097089</v>
       </c>
       <c r="D18" s="4">
-        <v>0.11638104838709677</v>
+        <v>8.2075143839054718E-2</v>
       </c>
       <c r="E18" s="4">
-        <v>0.10099402867665463</v>
+        <v>8.3290849960446514E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1849152273807637</v>
+        <v>1.1834765566108849</v>
       </c>
       <c r="C19" s="3">
         <v>1.1988727858293076</v>
       </c>
       <c r="D19" s="4">
-        <v>9.039345718091582E-2</v>
+        <v>8.8077122256304027E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.7093720416535181E-2</v>
@@ -867,13 +867,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1814698711250435</v>
+        <v>1.179654385392892</v>
       </c>
       <c r="C20" s="3">
         <v>1.2026419336706016</v>
       </c>
       <c r="D20" s="4">
-        <v>8.9386344531274323E-2</v>
+        <v>8.777151360787569E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.2934569674807371E-2</v>
@@ -884,13 +884,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2390571370886332</v>
+        <v>1.237810478778369</v>
       </c>
       <c r="C21" s="7">
         <v>1.2502607578248208</v>
       </c>
       <c r="D21" s="8">
-        <v>0.11093355073591746</v>
+        <v>0.10935781736378142</v>
       </c>
       <c r="E21" s="8">
         <v>0.10469837941728913</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0917B532-B9E4-4E94-827C-6797546EDB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88B21C8-B304-4042-94AA-F1ABA3C2EB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4060807268914903</v>
+        <v>1.4045893719806763</v>
       </c>
       <c r="C2" s="3">
         <v>1.4132687390660745</v>
       </c>
       <c r="D2" s="4">
-        <v>0.32555890551225897</v>
+        <v>0.3297115876898572</v>
       </c>
       <c r="E2" s="4">
         <v>0.12822238326948959</v>
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3670289855072464</v>
+        <v>1.3630210188813678</v>
       </c>
       <c r="C3" s="3">
         <v>1.3646732429099877</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1758970110254286</v>
+        <v>0.17889235867694858</v>
       </c>
       <c r="E3" s="4">
         <v>0.17409037243747988</v>
@@ -595,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3313650573115665</v>
+        <v>1.3291268758526602</v>
       </c>
       <c r="C4" s="3">
         <v>1.3190447030006125</v>
       </c>
       <c r="D4" s="4">
-        <v>0.21893536121673005</v>
+        <v>0.22296577946768062</v>
       </c>
       <c r="E4" s="4">
         <v>0.20724665270639001</v>
@@ -612,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2976114986260832</v>
+        <v>1.2975792988313857</v>
       </c>
       <c r="C5" s="3">
         <v>1.3368037480478916</v>
       </c>
       <c r="D5" s="4">
-        <v>8.4355609442978388E-2</v>
+        <v>8.5443263675914705E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.8249143324752375E-2</v>
@@ -629,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2520096852300242</v>
+        <v>1.250047700820454</v>
       </c>
       <c r="C6" s="3">
         <v>1.250354432491035</v>
       </c>
       <c r="D6" s="4">
-        <v>0.17266175019649158</v>
+        <v>0.17528721216073848</v>
       </c>
       <c r="E6" s="4">
         <v>0.13893909899888765</v>
@@ -646,13 +646,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2322834645669292</v>
+        <v>1.2335644937586685</v>
       </c>
       <c r="C7" s="3">
         <v>1.2246970994982256</v>
       </c>
       <c r="D7" s="4">
-        <v>9.8465968876336046E-2</v>
+        <v>9.9822783408096583E-2</v>
       </c>
       <c r="E7" s="4">
         <v>0.10209538565341797</v>
@@ -663,13 +663,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2287463160281114</v>
+        <v>1.228320160302794</v>
       </c>
       <c r="C8" s="3">
         <v>1.2016724053123464</v>
       </c>
       <c r="D8" s="4">
-        <v>9.9203850305865413E-2</v>
+        <v>0.1010143037063692</v>
       </c>
       <c r="E8" s="4">
         <v>9.078223204617257E-2</v>
@@ -680,13 +680,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2283757111343319</v>
+        <v>1.2265187049536668</v>
       </c>
       <c r="C9" s="3">
         <v>1.2383614555804026</v>
       </c>
       <c r="D9" s="4">
-        <v>0.11217034577065833</v>
+        <v>0.11383733802174904</v>
       </c>
       <c r="E9" s="4">
         <v>0.1095618860948393</v>
@@ -697,13 +697,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2246768507638073</v>
+        <v>1.2247972190034764</v>
       </c>
       <c r="C10" s="3">
         <v>1.2763180789977377</v>
       </c>
       <c r="D10" s="4">
-        <v>6.9784986797434931E-2</v>
+        <v>7.0769028914437537E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.4241054127373723E-2</v>
@@ -714,13 +714,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.210910005027652</v>
+        <v>1.2116428219042921</v>
       </c>
       <c r="C11" s="3">
         <v>1.2127823904228616</v>
       </c>
       <c r="D11" s="4">
-        <v>9.334303212333106E-2</v>
+        <v>9.5126358026139807E-2</v>
       </c>
       <c r="E11" s="4">
         <v>9.5866575347537161E-2</v>
@@ -731,13 +731,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2081081081081082</v>
+        <v>1.2084444444444442</v>
       </c>
       <c r="C12" s="3">
         <v>1.3470031545741326</v>
       </c>
       <c r="D12" s="4">
-        <v>8.8442691526234019E-2</v>
+        <v>8.9637863033345283E-2</v>
       </c>
       <c r="E12" s="4">
         <v>8.6934378060724779E-2</v>
@@ -748,13 +748,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2030723905723906</v>
+        <v>1.2021541010770505</v>
       </c>
       <c r="C13" s="3">
         <v>1.2116212338593972</v>
       </c>
       <c r="D13" s="4">
-        <v>9.8835274542429283E-2</v>
+        <v>0.10041597337770383</v>
       </c>
       <c r="E13" s="4">
         <v>0.10471361502347418</v>
@@ -765,13 +765,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1.1961471103327495</v>
+        <v>1.1968731905037637</v>
       </c>
       <c r="C14" s="3">
         <v>1.2359897172236505</v>
       </c>
       <c r="D14" s="4">
-        <v>8.4580062213005486E-2</v>
+        <v>8.5271317829457363E-2</v>
       </c>
       <c r="E14" s="4">
         <v>8.3397650287282396E-2</v>
@@ -782,13 +782,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1942421483841603</v>
+        <v>1.1943447037701975</v>
       </c>
       <c r="C15" s="3">
         <v>1.201725012683917</v>
       </c>
       <c r="D15" s="4">
-        <v>0.12548370054117344</v>
+        <v>0.12725429440406666</v>
       </c>
       <c r="E15" s="4">
         <v>0.12195423777054536</v>
@@ -796,36 +796,36 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1921955958549224</v>
+        <v>1.192009783938035</v>
       </c>
       <c r="C16" s="3">
-        <v>1.2233621574087645</v>
+        <v>1.1883519206939281</v>
       </c>
       <c r="D16" s="4">
-        <v>8.7523383028173002E-2</v>
+        <v>0.11499156197262329</v>
       </c>
       <c r="E16" s="4">
-        <v>8.4055042932994956E-2</v>
+        <v>0.10099402867665463</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1921884686918784</v>
+        <v>1.1915708812260537</v>
       </c>
       <c r="C17" s="3">
-        <v>1.1883519206939281</v>
+        <v>1.2233621574087645</v>
       </c>
       <c r="D17" s="4">
-        <v>0.11342115132195763</v>
+        <v>8.8770477864066666E-2</v>
       </c>
       <c r="E17" s="4">
-        <v>0.10099402867665463</v>
+        <v>8.4055042932994956E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -833,13 +833,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1912491178546225</v>
+        <v>1.1903106165971256</v>
       </c>
       <c r="C18" s="3">
         <v>1.2135922330097089</v>
       </c>
       <c r="D18" s="4">
-        <v>8.2075143839054718E-2</v>
+        <v>8.329150094605553E-2</v>
       </c>
       <c r="E18" s="4">
         <v>8.3290849960446514E-2</v>
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1834765566108849</v>
+        <v>1.1836977539788787</v>
       </c>
       <c r="C19" s="3">
         <v>1.1988727858293076</v>
       </c>
       <c r="D19" s="4">
-        <v>8.8077122256304027E-2</v>
+        <v>8.9272198542006936E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.7093720416535181E-2</v>
@@ -867,13 +867,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.179654385392892</v>
+        <v>1.1782273603082851</v>
       </c>
       <c r="C20" s="3">
         <v>1.2026419336706016</v>
       </c>
       <c r="D20" s="4">
-        <v>8.777151360787569E-2</v>
+        <v>8.9116561256904106E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.2934569674807371E-2</v>
@@ -884,13 +884,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.237810478778369</v>
+        <v>1.2371184555343979</v>
       </c>
       <c r="C21" s="7">
         <v>1.2502607578248208</v>
       </c>
       <c r="D21" s="8">
-        <v>0.10935781736378142</v>
+        <v>0.11099636401684584</v>
       </c>
       <c r="E21" s="8">
         <v>0.10469837941728913</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88B21C8-B304-4042-94AA-F1ABA3C2EB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED4705D-E6DF-40FC-B0ED-3D9E45CFD517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4045893719806763</v>
+        <v>1.4043855175930648</v>
       </c>
       <c r="C2" s="3">
         <v>1.4132687390660745</v>
       </c>
       <c r="D2" s="4">
-        <v>0.3297115876898572</v>
+        <v>0.33466067466863869</v>
       </c>
       <c r="E2" s="4">
         <v>0.12822238326948959</v>
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3630210188813678</v>
+        <v>1.3637630662020905</v>
       </c>
       <c r="C3" s="3">
         <v>1.3646732429099877</v>
       </c>
       <c r="D3" s="4">
-        <v>0.17889235867694858</v>
+        <v>0.18290739914600726</v>
       </c>
       <c r="E3" s="4">
         <v>0.17409037243747988</v>
@@ -595,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3291268758526602</v>
+        <v>1.3277675738854566</v>
       </c>
       <c r="C4" s="3">
         <v>1.3190447030006125</v>
       </c>
       <c r="D4" s="4">
-        <v>0.22296577946768062</v>
+        <v>0.22771863117870722</v>
       </c>
       <c r="E4" s="4">
         <v>0.20724665270639001</v>
@@ -612,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2975792988313857</v>
+        <v>1.2968234323432344</v>
       </c>
       <c r="C5" s="3">
         <v>1.3368037480478916</v>
       </c>
       <c r="D5" s="4">
-        <v>8.5443263675914705E-2</v>
+        <v>8.6441765922544753E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.8249143324752375E-2</v>
@@ -629,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.250047700820454</v>
+        <v>1.2504217432052485</v>
       </c>
       <c r="C6" s="3">
         <v>1.250354432491035</v>
       </c>
       <c r="D6" s="4">
-        <v>0.17528721216073848</v>
+        <v>0.17843107744276659</v>
       </c>
       <c r="E6" s="4">
         <v>0.13893909899888765</v>
@@ -646,13 +646,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2335644937586685</v>
+        <v>1.2320916905444126</v>
       </c>
       <c r="C7" s="3">
         <v>1.2246970994982256</v>
       </c>
       <c r="D7" s="4">
-        <v>9.9822783408096583E-2</v>
+        <v>0.10147034391094867</v>
       </c>
       <c r="E7" s="4">
         <v>0.10209538565341797</v>
@@ -663,13 +663,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>1.228320160302794</v>
+        <v>1.2272229522558038</v>
       </c>
       <c r="C8" s="3">
         <v>1.2016724053123464</v>
       </c>
       <c r="D8" s="4">
-        <v>0.1010143037063692</v>
+        <v>0.10268981648074847</v>
       </c>
       <c r="E8" s="4">
         <v>9.078223204617257E-2</v>
@@ -680,13 +680,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2265187049536668</v>
+        <v>1.2256028848320937</v>
       </c>
       <c r="C9" s="3">
         <v>1.2383614555804026</v>
       </c>
       <c r="D9" s="4">
-        <v>0.11383733802174904</v>
+        <v>0.11556944715764798</v>
       </c>
       <c r="E9" s="4">
         <v>0.1095618860948393</v>
@@ -697,13 +697,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2247972190034764</v>
+        <v>1.2227024567788898</v>
       </c>
       <c r="C10" s="3">
         <v>1.2763180789977377</v>
       </c>
       <c r="D10" s="4">
-        <v>7.0769028914437537E-2</v>
+        <v>7.2097485772391057E-2</v>
       </c>
       <c r="E10" s="4">
         <v>7.4241054127373723E-2</v>
@@ -714,13 +714,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2116428219042921</v>
+        <v>1.2109980620155039</v>
       </c>
       <c r="C11" s="3">
         <v>1.2127823904228616</v>
       </c>
       <c r="D11" s="4">
-        <v>9.5126358026139807E-2</v>
+        <v>9.6862754299927259E-2</v>
       </c>
       <c r="E11" s="4">
         <v>9.5866575347537161E-2</v>
@@ -731,13 +731,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2084444444444442</v>
+        <v>1.2089356110381078</v>
       </c>
       <c r="C12" s="3">
         <v>1.3470031545741326</v>
       </c>
       <c r="D12" s="4">
-        <v>8.9637863033345283E-2</v>
+        <v>9.0952551691167685E-2</v>
       </c>
       <c r="E12" s="4">
         <v>8.6934378060724779E-2</v>
@@ -748,13 +748,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>1.2021541010770505</v>
+        <v>1.201217038539554</v>
       </c>
       <c r="C13" s="3">
         <v>1.2116212338593972</v>
       </c>
       <c r="D13" s="4">
-        <v>0.10041597337770383</v>
+        <v>0.10253743760399335</v>
       </c>
       <c r="E13" s="4">
         <v>0.10471361502347418</v>
@@ -765,13 +765,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1.1968731905037637</v>
+        <v>1.1964692482915718</v>
       </c>
       <c r="C14" s="3">
         <v>1.2359897172236505</v>
       </c>
       <c r="D14" s="4">
-        <v>8.5271317829457363E-2</v>
+        <v>8.6703204463536271E-2</v>
       </c>
       <c r="E14" s="4">
         <v>8.3397650287282396E-2</v>
@@ -782,13 +782,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1943447037701975</v>
+        <v>1.1933348046788788</v>
       </c>
       <c r="C15" s="3">
         <v>1.201725012683917</v>
       </c>
       <c r="D15" s="4">
-        <v>0.12725429440406666</v>
+        <v>0.12939614181885684</v>
       </c>
       <c r="E15" s="4">
         <v>0.12195423777054536</v>
@@ -799,13 +799,13 @@
         <v>16</v>
       </c>
       <c r="B16" s="3">
-        <v>1.192009783938035</v>
+        <v>1.1919597989949748</v>
       </c>
       <c r="C16" s="3">
         <v>1.1883519206939281</v>
       </c>
       <c r="D16" s="4">
-        <v>0.11499156197262329</v>
+        <v>0.11660885055315957</v>
       </c>
       <c r="E16" s="4">
         <v>0.10099402867665463</v>
@@ -816,13 +816,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1.1915708812260537</v>
+        <v>1.191345397324941</v>
       </c>
       <c r="C17" s="3">
         <v>1.2233621574087645</v>
       </c>
       <c r="D17" s="4">
-        <v>8.8770477864066666E-2</v>
+        <v>9.0060087296638516E-2</v>
       </c>
       <c r="E17" s="4">
         <v>8.4055042932994956E-2</v>
@@ -833,13 +833,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1903106165971256</v>
+        <v>1.1902806297056809</v>
       </c>
       <c r="C18" s="3">
         <v>1.2135922330097089</v>
       </c>
       <c r="D18" s="4">
-        <v>8.329150094605553E-2</v>
+        <v>8.4623701587056413E-2</v>
       </c>
       <c r="E18" s="4">
         <v>8.3290849960446514E-2</v>
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1836977539788787</v>
+        <v>1.1822847924915678</v>
       </c>
       <c r="C19" s="3">
         <v>1.1988727858293076</v>
       </c>
       <c r="D19" s="4">
-        <v>8.9272198542006936E-2</v>
+        <v>9.0546946580090035E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.7093720416535181E-2</v>
@@ -867,13 +867,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1782273603082851</v>
+        <v>1.1772470144563167</v>
       </c>
       <c r="C20" s="3">
         <v>1.2026419336706016</v>
       </c>
       <c r="D20" s="4">
-        <v>8.9116561256904106E-2</v>
+        <v>9.1062587642732451E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.2934569674807371E-2</v>
@@ -884,13 +884,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.2371184555343979</v>
+        <v>1.236436623896759</v>
       </c>
       <c r="C21" s="7">
         <v>1.2502607578248208</v>
       </c>
       <c r="D21" s="8">
-        <v>0.11099636401684584</v>
+        <v>0.11286091710481572</v>
       </c>
       <c r="E21" s="8">
         <v>0.10469837941728913</v>

--- a/Conversion al 13062026.xlsx
+++ b/Conversion al 13062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\1 Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED4705D-E6DF-40FC-B0ED-3D9E45CFD517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B300F08-0B99-4218-9B40-94FD8E5A3378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>1.4043855175930648</v>
+        <v>1.4022299883508069</v>
       </c>
       <c r="C2" s="3">
         <v>1.4132687390660745</v>
       </c>
       <c r="D2" s="4">
-        <v>0.33466067466863869</v>
+        <v>0.32579700715679893</v>
       </c>
       <c r="E2" s="4">
         <v>0.12822238326948959</v>
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>1.3637630662020905</v>
+        <v>1.3594066082265677</v>
       </c>
       <c r="C3" s="3">
         <v>1.3646732429099877</v>
       </c>
       <c r="D3" s="4">
-        <v>0.18290739914600726</v>
+        <v>0.17644259369422963</v>
       </c>
       <c r="E3" s="4">
         <v>0.17409037243747988</v>
@@ -595,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>1.3277675738854566</v>
+        <v>1.3269736842105262</v>
       </c>
       <c r="C4" s="3">
         <v>1.3190447030006125</v>
       </c>
       <c r="D4" s="4">
-        <v>0.22771863117870722</v>
+        <v>0.21919388564424255</v>
       </c>
       <c r="E4" s="4">
         <v>0.20724665270639001</v>
@@ -612,13 +612,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>1.2968234323432344</v>
+        <v>1.2967256457189344</v>
       </c>
       <c r="C5" s="3">
         <v>1.3368037480478916</v>
       </c>
       <c r="D5" s="4">
-        <v>8.6441765922544753E-2</v>
+        <v>8.4057029540481401E-2</v>
       </c>
       <c r="E5" s="4">
         <v>9.8249143324752375E-2</v>
@@ -629,13 +629,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>1.2504217432052485</v>
+        <v>1.2500462534690102</v>
       </c>
       <c r="C6" s="3">
         <v>1.250354432491035</v>
       </c>
       <c r="D6" s="4">
-        <v>0.17843107744276659</v>
+        <v>0.18077225371661734</v>
       </c>
       <c r="E6" s="4">
         <v>0.13893909899888765</v>
@@ -646,13 +646,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>1.2320916905444126</v>
+        <v>1.2312760521715744</v>
       </c>
       <c r="C7" s="3">
         <v>1.2246970994982256</v>
       </c>
       <c r="D7" s="4">
-        <v>0.10147034391094867</v>
+        <v>9.8551608072830393E-2</v>
       </c>
       <c r="E7" s="4">
         <v>0.10209538565341797</v>
@@ -663,13 +663,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2272229522558038</v>
+        <v>1.2266163793103448</v>
       </c>
       <c r="C8" s="3">
         <v>1.2016724053123464</v>
       </c>
       <c r="D8" s="4">
-        <v>0.10268981648074847</v>
+        <v>0.10021814726020001</v>
       </c>
       <c r="E8" s="4">
         <v>9.078223204617257E-2</v>
@@ -677,36 +677,36 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1.2256028848320937</v>
+        <v>1.2245762711864407</v>
       </c>
       <c r="C9" s="3">
-        <v>1.2383614555804026</v>
+        <v>1.2763180789977377</v>
       </c>
       <c r="D9" s="4">
-        <v>0.11556944715764798</v>
+        <v>6.9854029381065885E-2</v>
       </c>
       <c r="E9" s="4">
-        <v>0.1095618860948393</v>
+        <v>7.4241054127373723E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="3">
-        <v>1.2227024567788898</v>
+        <v>1.2244920617297657</v>
       </c>
       <c r="C10" s="3">
-        <v>1.2763180789977377</v>
+        <v>1.2383614555804026</v>
       </c>
       <c r="D10" s="4">
-        <v>7.2097485772391057E-2</v>
+        <v>0.11242869446906245</v>
       </c>
       <c r="E10" s="4">
-        <v>7.4241054127373723E-2</v>
+        <v>0.1095618860948393</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -714,13 +714,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>1.2109980620155039</v>
+        <v>1.2102747909199523</v>
       </c>
       <c r="C11" s="3">
         <v>1.2127823904228616</v>
       </c>
       <c r="D11" s="4">
-        <v>9.6862754299927259E-2</v>
+        <v>9.4051284356248738E-2</v>
       </c>
       <c r="E11" s="4">
         <v>9.5866575347537161E-2</v>
@@ -731,13 +731,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>1.2089356110381078</v>
+        <v>1.2068074105988797</v>
       </c>
       <c r="C12" s="3">
         <v>1.3470031545741326</v>
       </c>
       <c r="D12" s="4">
-        <v>9.0952551691167685E-2</v>
+        <v>8.9009050467863171E-2</v>
       </c>
       <c r="E12" s="4">
         <v>8.6934378060724779E-2</v>
@@ -748,13 +748,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>1.201217038539554</v>
+        <v>1.1993658343242173</v>
       </c>
       <c r="C13" s="3">
         <v>1.2116212338593972</v>
       </c>
       <c r="D13" s="4">
-        <v>0.10253743760399335</v>
+        <v>9.9609143669311853E-2</v>
       </c>
       <c r="E13" s="4">
         <v>0.10471361502347418</v>
@@ -765,13 +765,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>1.1964692482915718</v>
+        <v>1.1969781757134861</v>
       </c>
       <c r="C14" s="3">
         <v>1.2359897172236505</v>
       </c>
       <c r="D14" s="4">
-        <v>8.6703204463536271E-2</v>
+        <v>8.5204787107233115E-2</v>
       </c>
       <c r="E14" s="4">
         <v>8.3397650287282396E-2</v>
@@ -779,36 +779,36 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="3">
-        <v>1.1933348046788788</v>
+        <v>1.1930761622156281</v>
       </c>
       <c r="C15" s="3">
-        <v>1.201725012683917</v>
+        <v>1.1883519206939281</v>
       </c>
       <c r="D15" s="4">
-        <v>0.12939614181885684</v>
+        <v>0.11368236405343408</v>
       </c>
       <c r="E15" s="4">
-        <v>0.12195423777054536</v>
+        <v>0.10099402867665463</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>1.1919597989949748</v>
+        <v>1.1929176623940909</v>
       </c>
       <c r="C16" s="3">
-        <v>1.1883519206939281</v>
+        <v>1.201725012683917</v>
       </c>
       <c r="D16" s="4">
-        <v>0.11660885055315957</v>
+        <v>0.12567746515405934</v>
       </c>
       <c r="E16" s="4">
-        <v>0.10099402867665463</v>
+        <v>0.12195423777054536</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -816,13 +816,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="3">
-        <v>1.191345397324941</v>
+        <v>1.1910512463229603</v>
       </c>
       <c r="C17" s="3">
         <v>1.2233621574087645</v>
       </c>
       <c r="D17" s="4">
-        <v>9.0060087296638516E-2</v>
+        <v>8.960628173469104E-2</v>
       </c>
       <c r="E17" s="4">
         <v>8.4055042932994956E-2</v>
@@ -833,13 +833,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>1.1902806297056809</v>
+        <v>1.1899641577060933</v>
       </c>
       <c r="C18" s="3">
         <v>1.2135922330097089</v>
       </c>
       <c r="D18" s="4">
-        <v>8.4623701587056413E-2</v>
+        <v>8.229481601651796E-2</v>
       </c>
       <c r="E18" s="4">
         <v>8.3290849960446514E-2</v>
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>1.1822847924915678</v>
+        <v>1.180901627538528</v>
       </c>
       <c r="C19" s="3">
         <v>1.1988727858293076</v>
       </c>
       <c r="D19" s="4">
-        <v>9.0546946580090035E-2</v>
+        <v>8.8217729946761872E-2</v>
       </c>
       <c r="E19" s="4">
         <v>8.7093720416535181E-2</v>
@@ -867,13 +867,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>1.1772470144563167</v>
+        <v>1.174892041949414</v>
       </c>
       <c r="C20" s="3">
         <v>1.2026419336706016</v>
       </c>
       <c r="D20" s="4">
-        <v>9.1062587642732451E-2</v>
+        <v>8.850910480766605E-2</v>
       </c>
       <c r="E20" s="4">
         <v>9.2934569674807371E-2</v>
@@ -884,13 +884,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="7">
-        <v>1.236436623896759</v>
+        <v>1.2357381173767981</v>
       </c>
       <c r="C21" s="7">
         <v>1.2502607578248208</v>
       </c>
       <c r="D21" s="8">
-        <v>0.11286091710481572</v>
+        <v>0.11022365661841321</v>
       </c>
       <c r="E21" s="8">
         <v>0.10469837941728913</v>
